--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127420363</v>
+        <v>127421466</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474460</v>
+        <v>474345</v>
       </c>
       <c r="R2" t="n">
-        <v>6861033</v>
+        <v>6861089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127420823</v>
+        <v>127420363</v>
       </c>
       <c r="B3" t="n">
         <v>98443</v>
@@ -800,29 +800,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474431</v>
+        <v>474460</v>
       </c>
       <c r="R3" t="n">
-        <v>6860959</v>
+        <v>6861033</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,48 +869,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127421466</v>
+        <v>127421372</v>
       </c>
       <c r="B4" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474345</v>
+        <v>474351</v>
       </c>
       <c r="R4" t="n">
-        <v>6861089</v>
+        <v>6861066</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,19 +963,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127421372</v>
+        <v>127420823</v>
       </c>
       <c r="B5" t="n">
         <v>98443</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474351</v>
+        <v>474431</v>
       </c>
       <c r="R5" t="n">
-        <v>6861066</v>
+        <v>6860959</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127419626</v>
+        <v>127421912</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474510</v>
+        <v>474304</v>
       </c>
       <c r="R8" t="n">
-        <v>6861060</v>
+        <v>6861121</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127419275</v>
+        <v>127420337</v>
       </c>
       <c r="B9" t="n">
-        <v>105478</v>
+        <v>79046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474510</v>
+        <v>474452</v>
       </c>
       <c r="R9" t="n">
-        <v>6861090</v>
+        <v>6861042</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127420337</v>
+        <v>127421390</v>
       </c>
       <c r="B10" t="n">
-        <v>79046</v>
+        <v>57817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,21 +1489,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474452</v>
+        <v>474349</v>
       </c>
       <c r="R10" t="n">
-        <v>6861042</v>
+        <v>6861060</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,6 +1549,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1575,45 +1580,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127420396</v>
+        <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474453</v>
+        <v>474342</v>
       </c>
       <c r="R11" t="n">
-        <v>6861008</v>
+        <v>6861153</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1672,32 +1686,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127421912</v>
+        <v>127422309</v>
       </c>
       <c r="B12" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474304</v>
+        <v>474479</v>
       </c>
       <c r="R12" t="n">
-        <v>6861121</v>
+        <v>6861149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1769,7 +1783,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422093</v>
+        <v>127419626</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1797,26 +1811,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474342</v>
+        <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861153</v>
+        <v>6861060</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1875,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127422309</v>
+        <v>127419275</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>105478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861149</v>
+        <v>6861090</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1960,22 +1965,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421390</v>
+        <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>78773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1988,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,13 +2012,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474349</v>
+        <v>474453</v>
       </c>
       <c r="R15" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2043,11 +2048,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2062,66 +2062,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127418924</v>
+        <v>127420119</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474504</v>
+        <v>474423</v>
       </c>
       <c r="R16" t="n">
-        <v>6861025</v>
+        <v>6861077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,7 +2171,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420119</v>
+        <v>127420234</v>
       </c>
       <c r="B17" t="n">
         <v>79046</v>
@@ -2220,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474423</v>
+        <v>474420</v>
       </c>
       <c r="R17" t="n">
-        <v>6861077</v>
+        <v>6861081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,45 +2268,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127420234</v>
+        <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474420</v>
+        <v>474504</v>
       </c>
       <c r="R18" t="n">
-        <v>6861081</v>
+        <v>6861025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R19" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R20" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,19 +2561,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R21" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B22" t="n">
         <v>79014</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R22" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,19 +2755,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127421540</v>
+        <v>127422329</v>
       </c>
       <c r="B23" t="n">
         <v>98443</v>
@@ -2795,26 +2795,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474339</v>
+        <v>474481</v>
       </c>
       <c r="R23" t="n">
-        <v>6861093</v>
+        <v>6861147</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2873,7 +2864,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127422329</v>
+        <v>127421540</v>
       </c>
       <c r="B24" t="n">
         <v>98443</v>
@@ -2901,17 +2892,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474481</v>
+        <v>474339</v>
       </c>
       <c r="R24" t="n">
-        <v>6861147</v>
+        <v>6861093</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2970,54 +2970,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127418605</v>
+        <v>127420142</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474512</v>
+        <v>474420</v>
       </c>
       <c r="R25" t="n">
-        <v>6861011</v>
+        <v>6861097</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3076,32 +3067,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420142</v>
+        <v>127421319</v>
       </c>
       <c r="B26" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3111,10 +3102,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474420</v>
+        <v>474350</v>
       </c>
       <c r="R26" t="n">
-        <v>6861097</v>
+        <v>6861063</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3173,7 +3164,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127419889</v>
+        <v>127420359</v>
       </c>
       <c r="B27" t="n">
         <v>98443</v>
@@ -3208,10 +3199,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474468</v>
+        <v>474456</v>
       </c>
       <c r="R27" t="n">
-        <v>6861065</v>
+        <v>6861021</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3270,7 +3261,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420359</v>
+        <v>127420283</v>
       </c>
       <c r="B28" t="n">
         <v>98443</v>
@@ -3298,20 +3289,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R28" t="n">
-        <v>6861021</v>
+        <v>6861057</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3355,19 +3355,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420283</v>
+        <v>127419889</v>
       </c>
       <c r="B29" t="n">
         <v>98443</v>
@@ -3395,29 +3395,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474434</v>
+        <v>474468</v>
       </c>
       <c r="R29" t="n">
-        <v>6861057</v>
+        <v>6861065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3461,60 +3452,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127421200</v>
+        <v>127418605</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474367</v>
+        <v>474512</v>
       </c>
       <c r="R30" t="n">
-        <v>6861033</v>
+        <v>6861011</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3558,12 +3558,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3676,32 +3676,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421319</v>
+        <v>127421200</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474350</v>
+        <v>474367</v>
       </c>
       <c r="R32" t="n">
-        <v>6861063</v>
+        <v>6861033</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3761,22 +3761,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R33" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B34" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R34" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419907</v>
+        <v>127420533</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474465</v>
+        <v>474406</v>
       </c>
       <c r="R35" t="n">
-        <v>6861092</v>
+        <v>6861004</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127418472</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474510</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861023</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127422311</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474481</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861140</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4232,6 +4232,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4246,12 +4251,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4355,10 +4360,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127422311</v>
+        <v>127419907</v>
       </c>
       <c r="B39" t="n">
-        <v>57817</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4371,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,13 +4395,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474481</v>
+        <v>474465</v>
       </c>
       <c r="R39" t="n">
-        <v>6861140</v>
+        <v>6861092</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4426,11 +4431,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4445,22 +4445,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127418472</v>
+        <v>127420169</v>
       </c>
       <c r="B40" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474510</v>
+        <v>474418</v>
       </c>
       <c r="R40" t="n">
-        <v>6861023</v>
+        <v>6861068</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R42" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R43" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5145,7 +5145,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127420285</v>
+        <v>127421249</v>
       </c>
       <c r="B47" t="n">
         <v>98443</v>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474453</v>
+        <v>474375</v>
       </c>
       <c r="R47" t="n">
-        <v>6861049</v>
+        <v>6861033</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,19 +5230,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127421425</v>
+        <v>127420285</v>
       </c>
       <c r="B48" t="n">
         <v>98443</v>
@@ -5270,29 +5270,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R48" t="n">
-        <v>6861090</v>
+        <v>6861049</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5336,19 +5327,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127421249</v>
+        <v>127421425</v>
       </c>
       <c r="B49" t="n">
         <v>98443</v>
@@ -5376,17 +5367,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474375</v>
+        <v>474343</v>
       </c>
       <c r="R49" t="n">
-        <v>6861033</v>
+        <v>6861090</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5542,54 +5542,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127418408</v>
+        <v>127422256</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474528</v>
+        <v>474414</v>
       </c>
       <c r="R51" t="n">
-        <v>6861030</v>
+        <v>6861137</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5648,10 +5639,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127420495</v>
+        <v>127418980</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5659,42 +5650,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474434</v>
+        <v>474490</v>
       </c>
       <c r="R52" t="n">
-        <v>6861012</v>
+        <v>6861042</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5724,11 +5710,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5743,44 +5724,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127418980</v>
+        <v>127418939</v>
       </c>
       <c r="B53" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5790,10 +5771,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474490</v>
+        <v>474503</v>
       </c>
       <c r="R53" t="n">
-        <v>6861042</v>
+        <v>6861040</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,48 +5833,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418939</v>
+        <v>127420495</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474503</v>
+        <v>474434</v>
       </c>
       <c r="R54" t="n">
-        <v>6861040</v>
+        <v>6861012</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5923,6 +5909,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5937,57 +5928,66 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127422256</v>
+        <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474414</v>
+        <v>474528</v>
       </c>
       <c r="R55" t="n">
-        <v>6861137</v>
+        <v>6861030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6734,32 +6734,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127420244</v>
+        <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474425</v>
+        <v>474358</v>
       </c>
       <c r="R63" t="n">
-        <v>6861027</v>
+        <v>6861062</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6819,44 +6819,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127419705</v>
+        <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,13 +6866,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474492</v>
+        <v>474344</v>
       </c>
       <c r="R64" t="n">
-        <v>6861034</v>
+        <v>6861094</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6916,19 +6916,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127420259</v>
+        <v>127419814</v>
       </c>
       <c r="B65" t="n">
         <v>98443</v>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474440</v>
+        <v>474459</v>
       </c>
       <c r="R65" t="n">
-        <v>6861055</v>
+        <v>6861043</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127419814</v>
+        <v>127420244</v>
       </c>
       <c r="B66" t="n">
         <v>98443</v>
@@ -7062,29 +7062,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474459</v>
+        <v>474425</v>
       </c>
       <c r="R66" t="n">
-        <v>6861043</v>
+        <v>6861027</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7128,60 +7119,69 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127421023</v>
+        <v>127421449</v>
       </c>
       <c r="B67" t="n">
-        <v>79603</v>
+        <v>98443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474421</v>
+        <v>474343</v>
       </c>
       <c r="R67" t="n">
-        <v>6860999</v>
+        <v>6861086</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7225,57 +7225,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127421291</v>
+        <v>127420259</v>
       </c>
       <c r="B68" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474358</v>
+        <v>474440</v>
       </c>
       <c r="R68" t="n">
-        <v>6861062</v>
+        <v>6861055</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,32 +7343,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127420397</v>
+        <v>127419705</v>
       </c>
       <c r="B69" t="n">
-        <v>79603</v>
+        <v>98443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7369,13 +7378,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474453</v>
+        <v>474492</v>
       </c>
       <c r="R69" t="n">
-        <v>6861033</v>
+        <v>6861034</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7419,22 +7428,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127421619</v>
+        <v>127421023</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7442,21 +7451,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7466,10 +7475,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474344</v>
+        <v>474421</v>
       </c>
       <c r="R70" t="n">
-        <v>6861094</v>
+        <v>6860999</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7528,57 +7537,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127421449</v>
+        <v>127420397</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>79603</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R71" t="n">
-        <v>6861086</v>
+        <v>6861033</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,12 +7622,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R59" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127421194</v>
+        <v>127420549</v>
       </c>
       <c r="B60" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474366</v>
+        <v>474427</v>
       </c>
       <c r="R60" t="n">
-        <v>6861035</v>
+        <v>6861001</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6531,10 +6531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127420003</v>
+        <v>127421194</v>
       </c>
       <c r="B61" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474452</v>
+        <v>474366</v>
       </c>
       <c r="R61" t="n">
-        <v>6861105</v>
+        <v>6861035</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127421023</v>
+        <v>127420397</v>
       </c>
       <c r="B70" t="n">
         <v>79603</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474421</v>
+        <v>474453</v>
       </c>
       <c r="R70" t="n">
-        <v>6860999</v>
+        <v>6861033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127420397</v>
+        <v>127421023</v>
       </c>
       <c r="B71" t="n">
         <v>79603</v>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474453</v>
+        <v>474421</v>
       </c>
       <c r="R71" t="n">
-        <v>6861033</v>
+        <v>6860999</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B19" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R19" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R20" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R42" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R43" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4845,57 +4845,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421641</v>
+        <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>91346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474318</v>
+        <v>474359</v>
       </c>
       <c r="R44" t="n">
-        <v>6861123</v>
+        <v>6861047</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4939,22 +4930,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421261</v>
+        <v>127422314</v>
       </c>
       <c r="B45" t="n">
-        <v>91346</v>
+        <v>57817</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4953,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474359</v>
+        <v>474474</v>
       </c>
       <c r="R45" t="n">
-        <v>6861047</v>
+        <v>6861148</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,48 +5039,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127422314</v>
+        <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474474</v>
+        <v>474318</v>
       </c>
       <c r="R46" t="n">
-        <v>6861148</v>
+        <v>6861123</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,12 +5133,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5736,48 +5736,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127418939</v>
+        <v>127420495</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474503</v>
+        <v>474434</v>
       </c>
       <c r="R53" t="n">
-        <v>6861040</v>
+        <v>6861012</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5807,6 +5812,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5821,65 +5831,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127420495</v>
+        <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474434</v>
+        <v>474503</v>
       </c>
       <c r="R54" t="n">
-        <v>6861012</v>
+        <v>6861040</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5909,11 +5914,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5928,12 +5928,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B59" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R59" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420549</v>
+        <v>127421194</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474427</v>
+        <v>474366</v>
       </c>
       <c r="R60" t="n">
-        <v>6861001</v>
+        <v>6861035</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6531,10 +6531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127421194</v>
+        <v>127420003</v>
       </c>
       <c r="B61" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474366</v>
+        <v>474452</v>
       </c>
       <c r="R61" t="n">
-        <v>6861035</v>
+        <v>6861105</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421291</v>
+        <v>127420397</v>
       </c>
       <c r="B63" t="n">
-        <v>79046</v>
+        <v>79603</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474358</v>
+        <v>474453</v>
       </c>
       <c r="R63" t="n">
-        <v>6861062</v>
+        <v>6861033</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R64" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,54 +6928,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127419814</v>
+        <v>127421619</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474459</v>
+        <v>474344</v>
       </c>
       <c r="R65" t="n">
-        <v>6861043</v>
+        <v>6861094</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7034,7 +7025,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420244</v>
+        <v>127419814</v>
       </c>
       <c r="B66" t="n">
         <v>98443</v>
@@ -7062,20 +7053,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474425</v>
+        <v>474459</v>
       </c>
       <c r="R66" t="n">
-        <v>6861027</v>
+        <v>6861043</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,19 +7119,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127421449</v>
+        <v>127420244</v>
       </c>
       <c r="B67" t="n">
         <v>98443</v>
@@ -7159,26 +7159,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474343</v>
+        <v>474425</v>
       </c>
       <c r="R67" t="n">
-        <v>6861086</v>
+        <v>6861027</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7237,7 +7228,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420259</v>
+        <v>127421449</v>
       </c>
       <c r="B68" t="n">
         <v>98443</v>
@@ -7267,7 +7258,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7281,13 +7272,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474440</v>
+        <v>474343</v>
       </c>
       <c r="R68" t="n">
-        <v>6861055</v>
+        <v>6861086</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7331,19 +7322,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127419705</v>
+        <v>127420259</v>
       </c>
       <c r="B69" t="n">
         <v>98443</v>
@@ -7371,20 +7362,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474492</v>
+        <v>474440</v>
       </c>
       <c r="R69" t="n">
-        <v>6861034</v>
+        <v>6861055</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,44 +7428,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420397</v>
+        <v>127419705</v>
       </c>
       <c r="B70" t="n">
-        <v>79603</v>
+        <v>98443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7475,13 +7475,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474453</v>
+        <v>474492</v>
       </c>
       <c r="R70" t="n">
-        <v>6861033</v>
+        <v>6861034</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7525,12 +7525,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421466</v>
       </c>
       <c r="B2" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127421372</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421912</v>
+        <v>127420337</v>
       </c>
       <c r="B8" t="n">
-        <v>92616</v>
+        <v>79050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474304</v>
+        <v>474452</v>
       </c>
       <c r="R8" t="n">
-        <v>6861121</v>
+        <v>6861042</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,44 +1369,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127420337</v>
+        <v>127419275</v>
       </c>
       <c r="B9" t="n">
-        <v>79046</v>
+        <v>105484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474452</v>
+        <v>474510</v>
       </c>
       <c r="R9" t="n">
-        <v>6861042</v>
+        <v>6861090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421390</v>
+        <v>127421912</v>
       </c>
       <c r="B10" t="n">
-        <v>57817</v>
+        <v>92620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474349</v>
+        <v>474304</v>
       </c>
       <c r="R10" t="n">
-        <v>6861060</v>
+        <v>6861121</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,11 +1549,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,69 +1563,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127422093</v>
+        <v>127421390</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474342</v>
+        <v>474349</v>
       </c>
       <c r="R11" t="n">
-        <v>6861153</v>
+        <v>6861060</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,6 +1646,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,22 +1665,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422309</v>
+        <v>127422093</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,17 +1705,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474479</v>
+        <v>474342</v>
       </c>
       <c r="R12" t="n">
-        <v>6861149</v>
+        <v>6861153</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419626</v>
+        <v>127422309</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R13" t="n">
-        <v>6861060</v>
+        <v>6861149</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419275</v>
+        <v>127419626</v>
       </c>
       <c r="B14" t="n">
-        <v>105478</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861090</v>
+        <v>6861060</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,12 +1965,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
         <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>127420119</v>
       </c>
       <c r="B16" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>127420234</v>
       </c>
       <c r="B17" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>79050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R19" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>79046</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R20" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2576,7 +2576,7 @@
         <v>127421356</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127421589</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420142</v>
+        <v>127421319</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474420</v>
+        <v>474350</v>
       </c>
       <c r="R25" t="n">
-        <v>6861097</v>
+        <v>6861063</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421319</v>
+        <v>127420359</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474350</v>
+        <v>474456</v>
       </c>
       <c r="R26" t="n">
-        <v>6861063</v>
+        <v>6861021</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,22 +3152,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420359</v>
+        <v>127420283</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3192,20 +3192,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R27" t="n">
-        <v>6861021</v>
+        <v>6861057</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,22 +3258,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420283</v>
+        <v>127419889</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3289,29 +3298,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474434</v>
+        <v>474468</v>
       </c>
       <c r="R28" t="n">
-        <v>6861057</v>
+        <v>6861065</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3355,22 +3355,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419889</v>
+        <v>127418605</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,20 +3395,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474468</v>
+        <v>474512</v>
       </c>
       <c r="R29" t="n">
-        <v>6861065</v>
+        <v>6861011</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3452,22 +3461,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127418605</v>
+        <v>127421355</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,7 +3503,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3508,13 +3517,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474512</v>
+        <v>474346</v>
       </c>
       <c r="R30" t="n">
-        <v>6861011</v>
+        <v>6861064</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3558,66 +3567,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421355</v>
+        <v>127421200</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>78777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474346</v>
+        <v>474367</v>
       </c>
       <c r="R31" t="n">
-        <v>6861064</v>
+        <v>6861033</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421200</v>
+        <v>127420142</v>
       </c>
       <c r="B32" t="n">
-        <v>78773</v>
+        <v>79636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3687,21 +3687,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474367</v>
+        <v>474420</v>
       </c>
       <c r="R32" t="n">
-        <v>6861033</v>
+        <v>6861097</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3761,22 +3761,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R33" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R34" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127420533</v>
+        <v>127420169</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474406</v>
+        <v>474418</v>
       </c>
       <c r="R35" t="n">
-        <v>6861004</v>
+        <v>6861068</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127418472</v>
+        <v>127420533</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474510</v>
+        <v>474406</v>
       </c>
       <c r="R36" t="n">
-        <v>6861023</v>
+        <v>6861004</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127422311</v>
+        <v>127418472</v>
       </c>
       <c r="B37" t="n">
-        <v>57817</v>
+        <v>80121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474481</v>
+        <v>474510</v>
       </c>
       <c r="R37" t="n">
-        <v>6861140</v>
+        <v>6861023</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4232,11 +4232,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4263,32 +4258,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127421991</v>
+        <v>127422311</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>57821</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4298,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474302</v>
+        <v>474481</v>
       </c>
       <c r="R38" t="n">
-        <v>6861119</v>
+        <v>6861140</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4334,6 +4329,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4348,12 +4348,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4363,7 +4363,7 @@
         <v>127419907</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4457,32 +4457,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420169</v>
+        <v>127421991</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474418</v>
+        <v>474302</v>
       </c>
       <c r="R40" t="n">
-        <v>6861068</v>
+        <v>6861119</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4845,48 +4845,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421261</v>
+        <v>127421641</v>
       </c>
       <c r="B44" t="n">
-        <v>91346</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474359</v>
+        <v>474318</v>
       </c>
       <c r="R44" t="n">
-        <v>6861047</v>
+        <v>6861123</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4930,12 +4939,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -4945,7 +4954,7 @@
         <v>127422314</v>
       </c>
       <c r="B45" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5039,57 +5048,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421641</v>
+        <v>127421261</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>91350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474318</v>
+        <v>474359</v>
       </c>
       <c r="R46" t="n">
-        <v>6861123</v>
+        <v>6861047</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,44 +5133,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421249</v>
+        <v>127421794</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>79050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474375</v>
+        <v>474313</v>
       </c>
       <c r="R47" t="n">
-        <v>6861033</v>
+        <v>6861110</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,22 +5230,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127420285</v>
+        <v>127421249</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474453</v>
+        <v>474375</v>
       </c>
       <c r="R48" t="n">
-        <v>6861049</v>
+        <v>6861033</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,22 +5327,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127421425</v>
+        <v>127420285</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,29 +5367,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R49" t="n">
-        <v>6861090</v>
+        <v>6861049</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5433,60 +5424,69 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421794</v>
+        <v>127421425</v>
       </c>
       <c r="B50" t="n">
-        <v>79046</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474313</v>
+        <v>474343</v>
       </c>
       <c r="R50" t="n">
-        <v>6861110</v>
+        <v>6861090</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5530,12 +5530,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5545,7 +5545,7 @@
         <v>127422256</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>127418980</v>
       </c>
       <c r="B52" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>127420495</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>127420040</v>
       </c>
       <c r="B56" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
         <v>127420549</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127421194</v>
+        <v>127420003</v>
       </c>
       <c r="B60" t="n">
-        <v>78772</v>
+        <v>79636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474366</v>
+        <v>474452</v>
       </c>
       <c r="R60" t="n">
-        <v>6861035</v>
+        <v>6861105</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,22 +6519,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127420003</v>
+        <v>127421194</v>
       </c>
       <c r="B61" t="n">
-        <v>79632</v>
+        <v>78776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474452</v>
+        <v>474366</v>
       </c>
       <c r="R61" t="n">
-        <v>6861105</v>
+        <v>6861035</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127420397</v>
+        <v>127421619</v>
       </c>
       <c r="B63" t="n">
-        <v>79603</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474453</v>
+        <v>474344</v>
       </c>
       <c r="R63" t="n">
-        <v>6861033</v>
+        <v>6861094</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6834,7 +6834,7 @@
         <v>127421291</v>
       </c>
       <c r="B64" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6928,45 +6928,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127421619</v>
+        <v>127419814</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474344</v>
+        <v>474459</v>
       </c>
       <c r="R65" t="n">
-        <v>6861094</v>
+        <v>6861043</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7025,10 +7034,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127419814</v>
+        <v>127420244</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7053,29 +7062,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474459</v>
+        <v>474425</v>
       </c>
       <c r="R66" t="n">
-        <v>6861043</v>
+        <v>6861027</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,22 +7119,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127420244</v>
+        <v>127421449</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,17 +7159,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474425</v>
+        <v>474343</v>
       </c>
       <c r="R67" t="n">
-        <v>6861027</v>
+        <v>6861086</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7228,10 +7237,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127421449</v>
+        <v>127420259</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7258,7 +7267,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7272,13 +7281,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474343</v>
+        <v>474440</v>
       </c>
       <c r="R68" t="n">
-        <v>6861086</v>
+        <v>6861055</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7322,22 +7331,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127420259</v>
+        <v>127419705</v>
       </c>
       <c r="B69" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7362,29 +7371,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474440</v>
+        <v>474492</v>
       </c>
       <c r="R69" t="n">
-        <v>6861055</v>
+        <v>6861034</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,44 +7428,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127419705</v>
+        <v>127420397</v>
       </c>
       <c r="B70" t="n">
-        <v>98443</v>
+        <v>79607</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7475,13 +7475,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474492</v>
+        <v>474453</v>
       </c>
       <c r="R70" t="n">
-        <v>6861034</v>
+        <v>6861033</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7525,12 +7525,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7540,7 +7540,7 @@
         <v>127421023</v>
       </c>
       <c r="B71" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127421466</v>
+        <v>127420363</v>
       </c>
       <c r="B2" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474345</v>
+        <v>474460</v>
       </c>
       <c r="R2" t="n">
-        <v>6861089</v>
+        <v>6861033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127420363</v>
+        <v>127421372</v>
       </c>
       <c r="B3" t="n">
         <v>98447</v>
@@ -800,20 +800,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474460</v>
+        <v>474351</v>
       </c>
       <c r="R3" t="n">
-        <v>6861033</v>
+        <v>6861066</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,19 +866,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127421372</v>
+        <v>127420823</v>
       </c>
       <c r="B4" t="n">
         <v>98447</v>
@@ -899,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -913,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474351</v>
+        <v>474431</v>
       </c>
       <c r="R4" t="n">
-        <v>6861066</v>
+        <v>6860959</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,69 +972,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127420823</v>
+        <v>127421466</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474431</v>
+        <v>474345</v>
       </c>
       <c r="R5" t="n">
-        <v>6860959</v>
+        <v>6861089</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127419275</v>
+        <v>127421390</v>
       </c>
       <c r="B9" t="n">
-        <v>105484</v>
+        <v>57821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474510</v>
+        <v>474349</v>
       </c>
       <c r="R9" t="n">
-        <v>6861090</v>
+        <v>6861060</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,6 +1452,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1478,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421912</v>
+        <v>127419275</v>
       </c>
       <c r="B10" t="n">
-        <v>92620</v>
+        <v>105484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1518,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474304</v>
+        <v>474510</v>
       </c>
       <c r="R10" t="n">
-        <v>6861121</v>
+        <v>6861090</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1563,60 +1568,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127421390</v>
+        <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474349</v>
+        <v>474342</v>
       </c>
       <c r="R11" t="n">
-        <v>6861060</v>
+        <v>6861153</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,11 +1660,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,19 +1674,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422093</v>
+        <v>127422309</v>
       </c>
       <c r="B12" t="n">
         <v>98447</v>
@@ -1705,26 +1714,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474342</v>
+        <v>474479</v>
       </c>
       <c r="R12" t="n">
-        <v>6861153</v>
+        <v>6861149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422309</v>
+        <v>127419626</v>
       </c>
       <c r="B13" t="n">
         <v>98447</v>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861149</v>
+        <v>6861060</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419626</v>
+        <v>127420396</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474510</v>
+        <v>474453</v>
       </c>
       <c r="R14" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1977,32 +1977,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420396</v>
+        <v>127421912</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474453</v>
+        <v>474304</v>
       </c>
       <c r="R15" t="n">
-        <v>6861008</v>
+        <v>6861121</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2074,45 +2074,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420119</v>
+        <v>127418924</v>
       </c>
       <c r="B16" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474423</v>
+        <v>474504</v>
       </c>
       <c r="R16" t="n">
-        <v>6861077</v>
+        <v>6861025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420234</v>
+        <v>127420119</v>
       </c>
       <c r="B17" t="n">
         <v>79050</v>
@@ -2206,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474420</v>
+        <v>474423</v>
       </c>
       <c r="R17" t="n">
-        <v>6861081</v>
+        <v>6861077</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,54 +2282,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127418924</v>
+        <v>127420234</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474504</v>
+        <v>474420</v>
       </c>
       <c r="R18" t="n">
-        <v>6861025</v>
+        <v>6861081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3773,10 +3773,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R33" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R34" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,44 +3955,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127420169</v>
+        <v>127421991</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474418</v>
+        <v>474302</v>
       </c>
       <c r="R35" t="n">
-        <v>6861068</v>
+        <v>6861119</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420533</v>
+        <v>127420169</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474406</v>
+        <v>474418</v>
       </c>
       <c r="R36" t="n">
-        <v>6861004</v>
+        <v>6861068</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127418472</v>
+        <v>127420533</v>
       </c>
       <c r="B37" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474510</v>
+        <v>474406</v>
       </c>
       <c r="R37" t="n">
-        <v>6861023</v>
+        <v>6861004</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127422311</v>
+        <v>127418472</v>
       </c>
       <c r="B38" t="n">
-        <v>57821</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474481</v>
+        <v>474510</v>
       </c>
       <c r="R38" t="n">
-        <v>6861140</v>
+        <v>6861023</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4329,11 +4329,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4360,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127419907</v>
+        <v>127422311</v>
       </c>
       <c r="B39" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4371,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4395,13 +4390,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474465</v>
+        <v>474481</v>
       </c>
       <c r="R39" t="n">
-        <v>6861092</v>
+        <v>6861140</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4431,6 +4426,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4445,44 +4445,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127421991</v>
+        <v>127419907</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474302</v>
+        <v>474465</v>
       </c>
       <c r="R40" t="n">
-        <v>6861119</v>
+        <v>6861092</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R42" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R43" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4845,57 +4845,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421641</v>
+        <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>91350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474318</v>
+        <v>474359</v>
       </c>
       <c r="R44" t="n">
-        <v>6861123</v>
+        <v>6861047</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4939,12 +4930,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5048,48 +5039,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421261</v>
+        <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>91350</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474359</v>
+        <v>474318</v>
       </c>
       <c r="R46" t="n">
-        <v>6861047</v>
+        <v>6861123</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,12 +5133,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5542,45 +5542,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127422256</v>
+        <v>127418408</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474414</v>
+        <v>474528</v>
       </c>
       <c r="R51" t="n">
-        <v>6861137</v>
+        <v>6861030</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5639,10 +5648,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418980</v>
+        <v>127422256</v>
       </c>
       <c r="B52" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5650,21 +5659,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5674,10 +5683,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474490</v>
+        <v>474414</v>
       </c>
       <c r="R52" t="n">
-        <v>6861042</v>
+        <v>6861137</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5736,10 +5745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127420495</v>
+        <v>127418980</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5747,42 +5756,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474434</v>
+        <v>474490</v>
       </c>
       <c r="R53" t="n">
-        <v>6861012</v>
+        <v>6861042</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5812,11 +5816,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5831,60 +5830,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418939</v>
+        <v>127420495</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474503</v>
+        <v>474434</v>
       </c>
       <c r="R54" t="n">
-        <v>6861040</v>
+        <v>6861012</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5914,6 +5918,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5928,19 +5937,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418408</v>
+        <v>127418939</v>
       </c>
       <c r="B55" t="n">
         <v>98447</v>
@@ -5968,26 +5977,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474528</v>
+        <v>474503</v>
       </c>
       <c r="R55" t="n">
-        <v>6861030</v>
+        <v>6861040</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R59" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B60" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R60" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,12 +6519,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R63" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421291</v>
+        <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474358</v>
+        <v>474344</v>
       </c>
       <c r="R64" t="n">
-        <v>6861062</v>
+        <v>6861094</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127420363</v>
+        <v>127421466</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474460</v>
+        <v>474345</v>
       </c>
       <c r="R2" t="n">
-        <v>6861033</v>
+        <v>6861089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127421372</v>
+        <v>127420363</v>
       </c>
       <c r="B3" t="n">
         <v>98447</v>
@@ -800,29 +800,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474351</v>
+        <v>474460</v>
       </c>
       <c r="R3" t="n">
-        <v>6861066</v>
+        <v>6861033</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127420823</v>
+        <v>127421372</v>
       </c>
       <c r="B4" t="n">
         <v>98447</v>
@@ -908,7 +899,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -922,13 +913,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474431</v>
+        <v>474351</v>
       </c>
       <c r="R4" t="n">
-        <v>6860959</v>
+        <v>6861066</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,60 +963,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127421466</v>
+        <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474345</v>
+        <v>474431</v>
       </c>
       <c r="R5" t="n">
-        <v>6861089</v>
+        <v>6860959</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420337</v>
+        <v>127421912</v>
       </c>
       <c r="B8" t="n">
-        <v>79050</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474452</v>
+        <v>474304</v>
       </c>
       <c r="R8" t="n">
-        <v>6861042</v>
+        <v>6861121</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,22 +1369,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421390</v>
+        <v>127420337</v>
       </c>
       <c r="B9" t="n">
-        <v>57821</v>
+        <v>79050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,21 +1392,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474349</v>
+        <v>474452</v>
       </c>
       <c r="R9" t="n">
-        <v>6861060</v>
+        <v>6861042</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,11 +1452,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127419275</v>
+        <v>127421390</v>
       </c>
       <c r="B10" t="n">
-        <v>105484</v>
+        <v>57821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474510</v>
+        <v>474349</v>
       </c>
       <c r="R10" t="n">
-        <v>6861090</v>
+        <v>6861060</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1554,6 +1549,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420396</v>
+        <v>127419275</v>
       </c>
       <c r="B14" t="n">
-        <v>78777</v>
+        <v>105484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474453</v>
+        <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861008</v>
+        <v>6861090</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,44 +1965,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421912</v>
+        <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474304</v>
+        <v>474453</v>
       </c>
       <c r="R15" t="n">
-        <v>6861121</v>
+        <v>6861008</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127421319</v>
+        <v>127421200</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474350</v>
+        <v>474367</v>
       </c>
       <c r="R25" t="n">
-        <v>6861063</v>
+        <v>6861033</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3055,44 +3055,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420359</v>
+        <v>127420142</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474456</v>
+        <v>474420</v>
       </c>
       <c r="R26" t="n">
-        <v>6861021</v>
+        <v>6861097</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,19 +3152,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420283</v>
+        <v>127421319</v>
       </c>
       <c r="B27" t="n">
         <v>98447</v>
@@ -3192,26 +3192,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474434</v>
+        <v>474350</v>
       </c>
       <c r="R27" t="n">
-        <v>6861057</v>
+        <v>6861063</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,7 +3261,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127419889</v>
+        <v>127420359</v>
       </c>
       <c r="B28" t="n">
         <v>98447</v>
@@ -3305,10 +3296,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474468</v>
+        <v>474456</v>
       </c>
       <c r="R28" t="n">
-        <v>6861065</v>
+        <v>6861021</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,7 +3358,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127418605</v>
+        <v>127420283</v>
       </c>
       <c r="B29" t="n">
         <v>98447</v>
@@ -3397,7 +3388,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3411,10 +3402,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474512</v>
+        <v>474434</v>
       </c>
       <c r="R29" t="n">
-        <v>6861011</v>
+        <v>6861057</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3473,7 +3464,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127421355</v>
+        <v>127419889</v>
       </c>
       <c r="B30" t="n">
         <v>98447</v>
@@ -3501,26 +3492,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474346</v>
+        <v>474468</v>
       </c>
       <c r="R30" t="n">
-        <v>6861064</v>
+        <v>6861065</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3579,48 +3561,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421200</v>
+        <v>127418605</v>
       </c>
       <c r="B31" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474367</v>
+        <v>474512</v>
       </c>
       <c r="R31" t="n">
-        <v>6861033</v>
+        <v>6861011</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3664,60 +3655,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127420142</v>
+        <v>127421355</v>
       </c>
       <c r="B32" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474420</v>
+        <v>474346</v>
       </c>
       <c r="R32" t="n">
-        <v>6861097</v>
+        <v>6861064</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421261</v>
+        <v>127422314</v>
       </c>
       <c r="B44" t="n">
-        <v>91350</v>
+        <v>57821</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4856,21 +4856,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474359</v>
+        <v>474474</v>
       </c>
       <c r="R44" t="n">
-        <v>6861047</v>
+        <v>6861148</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127422314</v>
+        <v>127421261</v>
       </c>
       <c r="B45" t="n">
-        <v>57821</v>
+        <v>91350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4953,21 +4953,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474474</v>
+        <v>474359</v>
       </c>
       <c r="R45" t="n">
-        <v>6861148</v>
+        <v>6861047</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421291</v>
+        <v>127421619</v>
       </c>
       <c r="B63" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474358</v>
+        <v>474344</v>
       </c>
       <c r="R63" t="n">
-        <v>6861062</v>
+        <v>6861094</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R64" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421912</v>
+        <v>127420396</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474304</v>
+        <v>474453</v>
       </c>
       <c r="R8" t="n">
-        <v>6861121</v>
+        <v>6861008</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127420337</v>
+        <v>127421912</v>
       </c>
       <c r="B9" t="n">
-        <v>79050</v>
+        <v>92620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474452</v>
+        <v>474304</v>
       </c>
       <c r="R9" t="n">
-        <v>6861042</v>
+        <v>6861121</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1466,22 +1466,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421390</v>
+        <v>127420337</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>79050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,21 +1489,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474349</v>
+        <v>474452</v>
       </c>
       <c r="R10" t="n">
-        <v>6861060</v>
+        <v>6861042</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,11 +1549,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,57 +1575,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127422093</v>
+        <v>127421390</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474342</v>
+        <v>474349</v>
       </c>
       <c r="R11" t="n">
-        <v>6861153</v>
+        <v>6861060</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,6 +1646,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,44 +1665,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422309</v>
+        <v>127419275</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>105484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,13 +1712,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R12" t="n">
-        <v>6861149</v>
+        <v>6861090</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,19 +1762,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419626</v>
+        <v>127422093</v>
       </c>
       <c r="B13" t="n">
         <v>98447</v>
@@ -1811,17 +1802,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474510</v>
+        <v>474342</v>
       </c>
       <c r="R13" t="n">
-        <v>6861060</v>
+        <v>6861153</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419275</v>
+        <v>127422309</v>
       </c>
       <c r="B14" t="n">
-        <v>105484</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R14" t="n">
-        <v>6861090</v>
+        <v>6861149</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,44 +1965,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420396</v>
+        <v>127419626</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474453</v>
+        <v>474510</v>
       </c>
       <c r="R15" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B19" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R19" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R20" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3967,32 +3967,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127421991</v>
+        <v>127420169</v>
       </c>
       <c r="B35" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474302</v>
+        <v>474418</v>
       </c>
       <c r="R35" t="n">
-        <v>6861119</v>
+        <v>6861068</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127418472</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474510</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861023</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,44 +4149,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127421991</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474302</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861119</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127418472</v>
+        <v>127419907</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474510</v>
+        <v>474465</v>
       </c>
       <c r="R38" t="n">
-        <v>6861023</v>
+        <v>6861092</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4343,22 +4343,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127422311</v>
+        <v>127420533</v>
       </c>
       <c r="B39" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,13 +4390,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474481</v>
+        <v>474406</v>
       </c>
       <c r="R39" t="n">
-        <v>6861140</v>
+        <v>6861004</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4426,11 +4426,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4445,22 +4440,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127419907</v>
+        <v>127422311</v>
       </c>
       <c r="B40" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4468,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,13 +4487,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474465</v>
+        <v>474481</v>
       </c>
       <c r="R40" t="n">
-        <v>6861092</v>
+        <v>6861140</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4528,6 +4523,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R63" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421291</v>
+        <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474358</v>
+        <v>474344</v>
       </c>
       <c r="R64" t="n">
-        <v>6861062</v>
+        <v>6861094</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127421372</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420396</v>
+        <v>127420337</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>79050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474453</v>
+        <v>474452</v>
       </c>
       <c r="R8" t="n">
-        <v>6861008</v>
+        <v>6861042</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,12 +1369,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127420337</v>
+        <v>127421390</v>
       </c>
       <c r="B10" t="n">
-        <v>79050</v>
+        <v>57821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,21 +1489,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474452</v>
+        <v>474349</v>
       </c>
       <c r="R10" t="n">
-        <v>6861042</v>
+        <v>6861060</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,6 +1549,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1575,48 +1580,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127421390</v>
+        <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474349</v>
+        <v>474342</v>
       </c>
       <c r="R11" t="n">
-        <v>6861060</v>
+        <v>6861153</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,11 +1660,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,44 +1674,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419275</v>
+        <v>127422309</v>
       </c>
       <c r="B12" t="n">
-        <v>105484</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,13 +1721,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R12" t="n">
-        <v>6861090</v>
+        <v>6861149</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1762,22 +1771,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422093</v>
+        <v>127419626</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,26 +1811,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474342</v>
+        <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861153</v>
+        <v>6861060</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127422309</v>
+        <v>127419275</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>105486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861149</v>
+        <v>6861090</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,44 +1965,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419626</v>
+        <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474510</v>
+        <v>474453</v>
       </c>
       <c r="R15" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2074,54 +2074,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127418924</v>
+        <v>127420119</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474504</v>
+        <v>474423</v>
       </c>
       <c r="R16" t="n">
-        <v>6861025</v>
+        <v>6861077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,7 +2171,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420119</v>
+        <v>127420234</v>
       </c>
       <c r="B17" t="n">
         <v>79050</v>
@@ -2220,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474423</v>
+        <v>474420</v>
       </c>
       <c r="R17" t="n">
-        <v>6861077</v>
+        <v>6861081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,45 +2268,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127420234</v>
+        <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474420</v>
+        <v>474504</v>
       </c>
       <c r="R18" t="n">
-        <v>6861081</v>
+        <v>6861025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R19" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R20" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127421200</v>
+        <v>127420142</v>
       </c>
       <c r="B25" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474367</v>
+        <v>474420</v>
       </c>
       <c r="R25" t="n">
-        <v>6861033</v>
+        <v>6861097</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3055,44 +3055,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420142</v>
+        <v>127421319</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474420</v>
+        <v>474350</v>
       </c>
       <c r="R26" t="n">
-        <v>6861097</v>
+        <v>6861063</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127421319</v>
+        <v>127420359</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474350</v>
+        <v>474456</v>
       </c>
       <c r="R27" t="n">
-        <v>6861063</v>
+        <v>6861021</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,22 +3249,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420359</v>
+        <v>127420283</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3289,20 +3289,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R28" t="n">
-        <v>6861021</v>
+        <v>6861057</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3346,22 +3355,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420283</v>
+        <v>127419889</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3386,29 +3395,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474434</v>
+        <v>474468</v>
       </c>
       <c r="R29" t="n">
-        <v>6861057</v>
+        <v>6861065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3452,22 +3452,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419889</v>
+        <v>127418605</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3492,20 +3492,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474468</v>
+        <v>474512</v>
       </c>
       <c r="R30" t="n">
-        <v>6861065</v>
+        <v>6861011</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3549,22 +3558,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127418605</v>
+        <v>127421355</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3591,7 +3600,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3605,13 +3614,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474512</v>
+        <v>474346</v>
       </c>
       <c r="R31" t="n">
-        <v>6861011</v>
+        <v>6861064</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3655,66 +3664,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421355</v>
+        <v>127421200</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474346</v>
+        <v>474367</v>
       </c>
       <c r="R32" t="n">
-        <v>6861064</v>
+        <v>6861033</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127420169</v>
+        <v>127422311</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474418</v>
+        <v>474481</v>
       </c>
       <c r="R35" t="n">
-        <v>6861068</v>
+        <v>6861140</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4038,6 +4038,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4052,22 +4057,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127418472</v>
+        <v>127420169</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4080,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4104,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474510</v>
+        <v>474418</v>
       </c>
       <c r="R36" t="n">
-        <v>6861023</v>
+        <v>6861068</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,44 +4154,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127421991</v>
+        <v>127420533</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474302</v>
+        <v>474406</v>
       </c>
       <c r="R37" t="n">
-        <v>6861119</v>
+        <v>6861004</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4258,10 +4263,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127419907</v>
+        <v>127418472</v>
       </c>
       <c r="B38" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4274,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4298,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474465</v>
+        <v>474510</v>
       </c>
       <c r="R38" t="n">
-        <v>6861092</v>
+        <v>6861023</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4343,44 +4348,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420533</v>
+        <v>127421991</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4395,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474406</v>
+        <v>474302</v>
       </c>
       <c r="R39" t="n">
-        <v>6861004</v>
+        <v>6861119</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4452,10 +4457,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127422311</v>
+        <v>127419907</v>
       </c>
       <c r="B40" t="n">
-        <v>57821</v>
+        <v>78777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,21 +4468,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,13 +4492,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474481</v>
+        <v>474465</v>
       </c>
       <c r="R40" t="n">
-        <v>6861140</v>
+        <v>6861092</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4523,11 +4528,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R42" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R43" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4845,48 +4845,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127422314</v>
+        <v>127421641</v>
       </c>
       <c r="B44" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474474</v>
+        <v>474318</v>
       </c>
       <c r="R44" t="n">
-        <v>6861148</v>
+        <v>6861123</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4930,12 +4939,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5039,57 +5048,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421641</v>
+        <v>127422314</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474318</v>
+        <v>474474</v>
       </c>
       <c r="R46" t="n">
-        <v>6861123</v>
+        <v>6861148</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,44 +5133,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421794</v>
+        <v>127421249</v>
       </c>
       <c r="B47" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474313</v>
+        <v>474375</v>
       </c>
       <c r="R47" t="n">
-        <v>6861110</v>
+        <v>6861033</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,22 +5230,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127421249</v>
+        <v>127420285</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474375</v>
+        <v>474453</v>
       </c>
       <c r="R48" t="n">
-        <v>6861033</v>
+        <v>6861049</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,22 +5327,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127420285</v>
+        <v>127421425</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,20 +5367,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474453</v>
+        <v>474343</v>
       </c>
       <c r="R49" t="n">
-        <v>6861049</v>
+        <v>6861090</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5424,69 +5433,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421425</v>
+        <v>127421794</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474343</v>
+        <v>474313</v>
       </c>
       <c r="R50" t="n">
-        <v>6861090</v>
+        <v>6861110</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5530,22 +5530,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127418408</v>
+        <v>127418939</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5570,26 +5570,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474528</v>
+        <v>474503</v>
       </c>
       <c r="R51" t="n">
-        <v>6861030</v>
+        <v>6861040</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5648,45 +5639,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127422256</v>
+        <v>127418408</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474414</v>
+        <v>474528</v>
       </c>
       <c r="R52" t="n">
-        <v>6861137</v>
+        <v>6861030</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127418980</v>
+        <v>127422256</v>
       </c>
       <c r="B53" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,21 +5756,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474490</v>
+        <v>474414</v>
       </c>
       <c r="R53" t="n">
-        <v>6861042</v>
+        <v>6861137</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127420495</v>
+        <v>127418980</v>
       </c>
       <c r="B54" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5853,42 +5853,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474434</v>
+        <v>474490</v>
       </c>
       <c r="R54" t="n">
-        <v>6861012</v>
+        <v>6861042</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5918,11 +5913,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5937,60 +5927,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418939</v>
+        <v>127420495</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474503</v>
+        <v>474434</v>
       </c>
       <c r="R55" t="n">
-        <v>6861040</v>
+        <v>6861012</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6020,6 +6015,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6034,12 +6034,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R59" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420549</v>
+        <v>127421194</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474427</v>
+        <v>474366</v>
       </c>
       <c r="R60" t="n">
-        <v>6861001</v>
+        <v>6861035</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6531,10 +6531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127421194</v>
+        <v>127420003</v>
       </c>
       <c r="B61" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474366</v>
+        <v>474452</v>
       </c>
       <c r="R61" t="n">
-        <v>6861035</v>
+        <v>6861105</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6734,45 +6734,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421291</v>
+        <v>127419814</v>
       </c>
       <c r="B63" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474358</v>
+        <v>474459</v>
       </c>
       <c r="R63" t="n">
-        <v>6861062</v>
+        <v>6861043</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,32 +6840,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421619</v>
+        <v>127420244</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,13 +6875,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474344</v>
+        <v>474425</v>
       </c>
       <c r="R64" t="n">
-        <v>6861094</v>
+        <v>6861027</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6916,22 +6925,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127419814</v>
+        <v>127421449</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6958,7 +6967,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6972,13 +6981,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474459</v>
+        <v>474343</v>
       </c>
       <c r="R65" t="n">
-        <v>6861043</v>
+        <v>6861086</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7022,22 +7031,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420244</v>
+        <v>127420259</v>
       </c>
       <c r="B66" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7062,20 +7071,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474425</v>
+        <v>474440</v>
       </c>
       <c r="R66" t="n">
-        <v>6861027</v>
+        <v>6861055</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,22 +7137,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127421449</v>
+        <v>127419705</v>
       </c>
       <c r="B67" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,26 +7177,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474343</v>
+        <v>474492</v>
       </c>
       <c r="R67" t="n">
-        <v>6861086</v>
+        <v>6861034</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7237,54 +7246,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420259</v>
+        <v>127421291</v>
       </c>
       <c r="B68" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474440</v>
+        <v>474358</v>
       </c>
       <c r="R68" t="n">
-        <v>6861055</v>
+        <v>6861062</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127419705</v>
+        <v>127421619</v>
       </c>
       <c r="B69" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474492</v>
+        <v>474344</v>
       </c>
       <c r="R69" t="n">
-        <v>6861034</v>
+        <v>6861094</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,12 +7428,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -4845,57 +4845,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421641</v>
+        <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>91350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474318</v>
+        <v>474359</v>
       </c>
       <c r="R44" t="n">
-        <v>6861123</v>
+        <v>6861047</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4939,22 +4930,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421261</v>
+        <v>127422314</v>
       </c>
       <c r="B45" t="n">
-        <v>91350</v>
+        <v>57821</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4953,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474359</v>
+        <v>474474</v>
       </c>
       <c r="R45" t="n">
-        <v>6861047</v>
+        <v>6861148</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,48 +5039,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127422314</v>
+        <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474474</v>
+        <v>474318</v>
       </c>
       <c r="R46" t="n">
-        <v>6861148</v>
+        <v>6861123</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,12 +5133,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5542,32 +5542,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127418939</v>
+        <v>127422256</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474503</v>
+        <v>474414</v>
       </c>
       <c r="R51" t="n">
-        <v>6861040</v>
+        <v>6861137</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5639,54 +5639,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418408</v>
+        <v>127418980</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474528</v>
+        <v>474490</v>
       </c>
       <c r="R52" t="n">
-        <v>6861030</v>
+        <v>6861042</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5745,10 +5736,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127422256</v>
+        <v>127420495</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,37 +5747,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474414</v>
+        <v>474434</v>
       </c>
       <c r="R53" t="n">
-        <v>6861137</v>
+        <v>6861012</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5816,6 +5812,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5830,44 +5831,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418980</v>
+        <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5877,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474490</v>
+        <v>474503</v>
       </c>
       <c r="R54" t="n">
-        <v>6861042</v>
+        <v>6861040</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,38 +5940,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127420495</v>
+        <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5979,13 +5984,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474434</v>
+        <v>474528</v>
       </c>
       <c r="R55" t="n">
-        <v>6861012</v>
+        <v>6861030</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6015,11 +6020,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6034,12 +6034,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6734,54 +6734,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127419814</v>
+        <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>98448</v>
+        <v>79050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474459</v>
+        <v>474358</v>
       </c>
       <c r="R63" t="n">
-        <v>6861043</v>
+        <v>6861062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6840,32 +6831,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127420244</v>
+        <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6875,13 +6866,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474425</v>
+        <v>474344</v>
       </c>
       <c r="R64" t="n">
-        <v>6861027</v>
+        <v>6861094</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6925,69 +6916,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127421449</v>
+        <v>127420397</v>
       </c>
       <c r="B65" t="n">
-        <v>98448</v>
+        <v>79607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R65" t="n">
-        <v>6861086</v>
+        <v>6861033</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7031,66 +7013,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420259</v>
+        <v>127421023</v>
       </c>
       <c r="B66" t="n">
-        <v>98448</v>
+        <v>79607</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474440</v>
+        <v>474421</v>
       </c>
       <c r="R66" t="n">
-        <v>6861055</v>
+        <v>6860999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7149,7 +7122,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127419705</v>
+        <v>127419814</v>
       </c>
       <c r="B67" t="n">
         <v>98448</v>
@@ -7177,20 +7150,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474492</v>
+        <v>474459</v>
       </c>
       <c r="R67" t="n">
-        <v>6861034</v>
+        <v>6861043</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7234,44 +7216,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127421291</v>
+        <v>127420244</v>
       </c>
       <c r="B68" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7281,13 +7263,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474358</v>
+        <v>474425</v>
       </c>
       <c r="R68" t="n">
-        <v>6861062</v>
+        <v>6861027</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7331,60 +7313,69 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127421619</v>
+        <v>127421449</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474344</v>
+        <v>474343</v>
       </c>
       <c r="R69" t="n">
-        <v>6861094</v>
+        <v>6861086</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,57 +7419,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420397</v>
+        <v>127420259</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>98448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474453</v>
+        <v>474440</v>
       </c>
       <c r="R70" t="n">
-        <v>6861033</v>
+        <v>6861055</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127421023</v>
+        <v>127419705</v>
       </c>
       <c r="B71" t="n">
-        <v>79607</v>
+        <v>98448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474421</v>
+        <v>474492</v>
       </c>
       <c r="R71" t="n">
-        <v>6860999</v>
+        <v>6861034</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,12 +7622,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421466</v>
       </c>
       <c r="B2" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127421372</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420337</v>
+        <v>127421912</v>
       </c>
       <c r="B8" t="n">
-        <v>79050</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474452</v>
+        <v>474304</v>
       </c>
       <c r="R8" t="n">
-        <v>6861042</v>
+        <v>6861121</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,44 +1369,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421912</v>
+        <v>127421390</v>
       </c>
       <c r="B9" t="n">
-        <v>92620</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474304</v>
+        <v>474349</v>
       </c>
       <c r="R9" t="n">
-        <v>6861121</v>
+        <v>6861060</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,6 +1452,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,22 +1471,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421390</v>
+        <v>127420337</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>79052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1518,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474349</v>
+        <v>474452</v>
       </c>
       <c r="R10" t="n">
-        <v>6861060</v>
+        <v>6861042</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,11 +1554,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,57 +1580,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127422093</v>
+        <v>127419275</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>105488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474342</v>
+        <v>474510</v>
       </c>
       <c r="R11" t="n">
-        <v>6861153</v>
+        <v>6861090</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,22 +1665,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422309</v>
+        <v>127422093</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,17 +1705,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474479</v>
+        <v>474342</v>
       </c>
       <c r="R12" t="n">
-        <v>6861149</v>
+        <v>6861153</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419626</v>
+        <v>127422309</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R13" t="n">
-        <v>6861060</v>
+        <v>6861149</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419275</v>
+        <v>127419626</v>
       </c>
       <c r="B14" t="n">
-        <v>105486</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861090</v>
+        <v>6861060</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,12 +1965,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
         <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,45 +2074,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420119</v>
+        <v>127418924</v>
       </c>
       <c r="B16" t="n">
-        <v>79050</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474423</v>
+        <v>474504</v>
       </c>
       <c r="R16" t="n">
-        <v>6861077</v>
+        <v>6861025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420234</v>
+        <v>127420119</v>
       </c>
       <c r="B17" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474420</v>
+        <v>474423</v>
       </c>
       <c r="R17" t="n">
-        <v>6861081</v>
+        <v>6861077</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,54 +2282,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127418924</v>
+        <v>127420234</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>79052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474504</v>
+        <v>474420</v>
       </c>
       <c r="R18" t="n">
-        <v>6861025</v>
+        <v>6861081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B19" t="n">
-        <v>79050</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R19" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>79052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R20" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,22 +2561,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R21" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,22 +2658,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R22" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>127420142</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>127421319</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>127420359</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>127420283</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>127419889</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>127418605</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>127421355</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>127421200</v>
       </c>
       <c r="B32" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B33" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R33" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R34" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127422311</v>
+        <v>127420169</v>
       </c>
       <c r="B35" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474481</v>
+        <v>474418</v>
       </c>
       <c r="R35" t="n">
-        <v>6861140</v>
+        <v>6861068</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4038,11 +4038,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,22 +4052,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127420533</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474406</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861004</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4166,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127418472</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4177,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4201,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474510</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861023</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4251,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127418472</v>
+        <v>127422311</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>57823</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4274,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4298,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474510</v>
+        <v>474481</v>
       </c>
       <c r="R38" t="n">
-        <v>6861023</v>
+        <v>6861140</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4334,6 +4329,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4363,7 +4363,7 @@
         <v>127421991</v>
       </c>
       <c r="B39" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>127419907</v>
       </c>
       <c r="B40" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R42" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R43" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421261</v>
+        <v>127422314</v>
       </c>
       <c r="B44" t="n">
-        <v>91350</v>
+        <v>57823</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4856,21 +4856,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474359</v>
+        <v>474474</v>
       </c>
       <c r="R44" t="n">
-        <v>6861047</v>
+        <v>6861148</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4942,48 +4942,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127422314</v>
+        <v>127421641</v>
       </c>
       <c r="B45" t="n">
-        <v>57821</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474474</v>
+        <v>474318</v>
       </c>
       <c r="R45" t="n">
-        <v>6861148</v>
+        <v>6861123</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5027,69 +5036,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421641</v>
+        <v>127421261</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>91352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474318</v>
+        <v>474359</v>
       </c>
       <c r="R46" t="n">
-        <v>6861123</v>
+        <v>6861047</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,12 +5133,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5148,7 +5148,7 @@
         <v>127421249</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,10 +5242,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127420285</v>
+        <v>127421425</v>
       </c>
       <c r="B48" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5270,20 +5270,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474453</v>
+        <v>474343</v>
       </c>
       <c r="R48" t="n">
-        <v>6861049</v>
+        <v>6861090</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,22 +5336,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127421425</v>
+        <v>127420285</v>
       </c>
       <c r="B49" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,29 +5376,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R49" t="n">
-        <v>6861090</v>
+        <v>6861049</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5433,12 +5433,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5448,7 +5448,7 @@
         <v>127421794</v>
       </c>
       <c r="B50" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127422256</v>
+        <v>127420495</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5553,37 +5553,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474414</v>
+        <v>474434</v>
       </c>
       <c r="R51" t="n">
-        <v>6861137</v>
+        <v>6861012</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5613,6 +5618,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5627,57 +5637,66 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418980</v>
+        <v>127418408</v>
       </c>
       <c r="B52" t="n">
-        <v>80121</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474490</v>
+        <v>474528</v>
       </c>
       <c r="R52" t="n">
-        <v>6861042</v>
+        <v>6861030</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5736,10 +5755,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127420495</v>
+        <v>127422256</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5747,42 +5766,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474434</v>
+        <v>474414</v>
       </c>
       <c r="R53" t="n">
-        <v>6861012</v>
+        <v>6861137</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5812,11 +5826,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5831,44 +5840,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418939</v>
+        <v>127418980</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>80123</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5878,10 +5887,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474503</v>
+        <v>474490</v>
       </c>
       <c r="R54" t="n">
-        <v>6861040</v>
+        <v>6861042</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,10 +5949,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418408</v>
+        <v>127418939</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5968,26 +5977,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474528</v>
+        <v>474503</v>
       </c>
       <c r="R55" t="n">
-        <v>6861030</v>
+        <v>6861040</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,7 +6049,7 @@
         <v>127420040</v>
       </c>
       <c r="B56" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R59" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127421194</v>
+        <v>127420549</v>
       </c>
       <c r="B60" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474366</v>
+        <v>474427</v>
       </c>
       <c r="R60" t="n">
-        <v>6861035</v>
+        <v>6861001</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6531,10 +6531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127420003</v>
+        <v>127421194</v>
       </c>
       <c r="B61" t="n">
-        <v>79636</v>
+        <v>78778</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474452</v>
+        <v>474366</v>
       </c>
       <c r="R61" t="n">
-        <v>6861105</v>
+        <v>6861035</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421291</v>
+        <v>127421619</v>
       </c>
       <c r="B63" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474358</v>
+        <v>474344</v>
       </c>
       <c r="R63" t="n">
-        <v>6861062</v>
+        <v>6861094</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421619</v>
+        <v>127420397</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>79609</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474344</v>
+        <v>474453</v>
       </c>
       <c r="R64" t="n">
-        <v>6861094</v>
+        <v>6861033</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,10 +6928,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127420397</v>
+        <v>127421023</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474453</v>
+        <v>474421</v>
       </c>
       <c r="R65" t="n">
-        <v>6861033</v>
+        <v>6860999</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127421023</v>
+        <v>127421291</v>
       </c>
       <c r="B66" t="n">
-        <v>79607</v>
+        <v>79052</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474421</v>
+        <v>474358</v>
       </c>
       <c r="R66" t="n">
-        <v>6860999</v>
+        <v>6861062</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7125,7 +7125,7 @@
         <v>127419814</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>127420244</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>127421449</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>127420259</v>
       </c>
       <c r="B70" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>127419705</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421912</v>
+        <v>127421390</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474304</v>
+        <v>474349</v>
       </c>
       <c r="R8" t="n">
-        <v>6861121</v>
+        <v>6861060</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1355,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,44 +1374,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421390</v>
+        <v>127419275</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>105488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1421,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474349</v>
+        <v>474510</v>
       </c>
       <c r="R9" t="n">
-        <v>6861060</v>
+        <v>6861090</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,11 +1457,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127420337</v>
+        <v>127420396</v>
       </c>
       <c r="B10" t="n">
-        <v>79052</v>
+        <v>78779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474452</v>
+        <v>474453</v>
       </c>
       <c r="R10" t="n">
-        <v>6861042</v>
+        <v>6861008</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1568,60 +1568,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419275</v>
+        <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>105488</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474510</v>
+        <v>474342</v>
       </c>
       <c r="R11" t="n">
-        <v>6861090</v>
+        <v>6861153</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1665,19 +1674,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422093</v>
+        <v>127422309</v>
       </c>
       <c r="B12" t="n">
         <v>98450</v>
@@ -1705,26 +1714,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474342</v>
+        <v>474479</v>
       </c>
       <c r="R12" t="n">
-        <v>6861153</v>
+        <v>6861149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422309</v>
+        <v>127419626</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861149</v>
+        <v>6861060</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419626</v>
+        <v>127420337</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474510</v>
+        <v>474452</v>
       </c>
       <c r="R14" t="n">
-        <v>6861060</v>
+        <v>6861042</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,44 +1965,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420396</v>
+        <v>127421912</v>
       </c>
       <c r="B15" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474453</v>
+        <v>474304</v>
       </c>
       <c r="R15" t="n">
-        <v>6861008</v>
+        <v>6861121</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2074,54 +2074,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127418924</v>
+        <v>127420119</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474504</v>
+        <v>474423</v>
       </c>
       <c r="R16" t="n">
-        <v>6861025</v>
+        <v>6861077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,7 +2171,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420119</v>
+        <v>127420234</v>
       </c>
       <c r="B17" t="n">
         <v>79052</v>
@@ -2220,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474423</v>
+        <v>474420</v>
       </c>
       <c r="R17" t="n">
-        <v>6861077</v>
+        <v>6861081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,45 +2268,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127420234</v>
+        <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>79052</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474420</v>
+        <v>474504</v>
       </c>
       <c r="R18" t="n">
-        <v>6861081</v>
+        <v>6861025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R19" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>79052</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R20" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,19 +2561,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B21" t="n">
         <v>79020</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R21" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R22" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3067,32 +3067,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421319</v>
+        <v>127421200</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474350</v>
+        <v>474367</v>
       </c>
       <c r="R26" t="n">
-        <v>6861063</v>
+        <v>6861033</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,19 +3152,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420359</v>
+        <v>127421319</v>
       </c>
       <c r="B27" t="n">
         <v>98450</v>
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474456</v>
+        <v>474350</v>
       </c>
       <c r="R27" t="n">
-        <v>6861021</v>
+        <v>6861063</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,19 +3249,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420283</v>
+        <v>127420359</v>
       </c>
       <c r="B28" t="n">
         <v>98450</v>
@@ -3289,29 +3289,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474434</v>
+        <v>474456</v>
       </c>
       <c r="R28" t="n">
-        <v>6861057</v>
+        <v>6861021</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3355,19 +3346,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419889</v>
+        <v>127420283</v>
       </c>
       <c r="B29" t="n">
         <v>98450</v>
@@ -3395,20 +3386,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474468</v>
+        <v>474434</v>
       </c>
       <c r="R29" t="n">
-        <v>6861065</v>
+        <v>6861057</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3452,19 +3452,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127418605</v>
+        <v>127419889</v>
       </c>
       <c r="B30" t="n">
         <v>98450</v>
@@ -3492,29 +3492,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474512</v>
+        <v>474468</v>
       </c>
       <c r="R30" t="n">
-        <v>6861011</v>
+        <v>6861065</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3558,19 +3549,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421355</v>
+        <v>127418605</v>
       </c>
       <c r="B31" t="n">
         <v>98450</v>
@@ -3600,7 +3591,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3614,13 +3605,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474346</v>
+        <v>474512</v>
       </c>
       <c r="R31" t="n">
-        <v>6861064</v>
+        <v>6861011</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3664,57 +3655,66 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421200</v>
+        <v>127421355</v>
       </c>
       <c r="B32" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474367</v>
+        <v>474346</v>
       </c>
       <c r="R32" t="n">
-        <v>6861033</v>
+        <v>6861064</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127420169</v>
+        <v>127418472</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474418</v>
+        <v>474510</v>
       </c>
       <c r="R35" t="n">
-        <v>6861068</v>
+        <v>6861023</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4052,19 +4052,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420533</v>
+        <v>127420169</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474406</v>
+        <v>474418</v>
       </c>
       <c r="R36" t="n">
-        <v>6861004</v>
+        <v>6861068</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127418472</v>
+        <v>127420533</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474510</v>
+        <v>474406</v>
       </c>
       <c r="R37" t="n">
-        <v>6861023</v>
+        <v>6861004</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127422311</v>
+        <v>127419907</v>
       </c>
       <c r="B38" t="n">
-        <v>57823</v>
+        <v>78779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474481</v>
+        <v>474465</v>
       </c>
       <c r="R38" t="n">
-        <v>6861140</v>
+        <v>6861092</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4329,11 +4329,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4348,12 +4343,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4457,10 +4452,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127419907</v>
+        <v>127422311</v>
       </c>
       <c r="B40" t="n">
-        <v>78779</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4468,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,13 +4487,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474465</v>
+        <v>474481</v>
       </c>
       <c r="R40" t="n">
-        <v>6861092</v>
+        <v>6861140</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4528,6 +4523,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R42" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R43" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127422314</v>
+        <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>57823</v>
+        <v>91352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4856,21 +4856,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474474</v>
+        <v>474359</v>
       </c>
       <c r="R44" t="n">
-        <v>6861148</v>
+        <v>6861047</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4942,57 +4942,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421641</v>
+        <v>127422314</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474318</v>
+        <v>474474</v>
       </c>
       <c r="R45" t="n">
-        <v>6861123</v>
+        <v>6861148</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5036,60 +5027,69 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421261</v>
+        <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>91352</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474359</v>
+        <v>474318</v>
       </c>
       <c r="R46" t="n">
-        <v>6861047</v>
+        <v>6861123</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,12 +5133,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5242,7 +5242,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127421425</v>
+        <v>127420285</v>
       </c>
       <c r="B48" t="n">
         <v>98450</v>
@@ -5270,29 +5270,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R48" t="n">
-        <v>6861090</v>
+        <v>6861049</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5336,19 +5327,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127420285</v>
+        <v>127421425</v>
       </c>
       <c r="B49" t="n">
         <v>98450</v>
@@ -5376,20 +5367,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474453</v>
+        <v>474343</v>
       </c>
       <c r="R49" t="n">
-        <v>6861049</v>
+        <v>6861090</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5433,12 +5433,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5542,10 +5542,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127420495</v>
+        <v>127422256</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5553,42 +5553,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474434</v>
+        <v>474414</v>
       </c>
       <c r="R51" t="n">
-        <v>6861012</v>
+        <v>6861137</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5618,11 +5613,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5637,66 +5627,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418408</v>
+        <v>127418980</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474528</v>
+        <v>474490</v>
       </c>
       <c r="R52" t="n">
-        <v>6861030</v>
+        <v>6861042</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,10 +5736,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127422256</v>
+        <v>127420495</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5766,37 +5747,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474414</v>
+        <v>474434</v>
       </c>
       <c r="R53" t="n">
-        <v>6861137</v>
+        <v>6861012</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5826,6 +5812,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5840,44 +5831,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418980</v>
+        <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5887,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474490</v>
+        <v>474503</v>
       </c>
       <c r="R54" t="n">
-        <v>6861042</v>
+        <v>6861040</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,7 +5940,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418939</v>
+        <v>127418408</v>
       </c>
       <c r="B55" t="n">
         <v>98450</v>
@@ -5977,17 +5968,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474503</v>
+        <v>474528</v>
       </c>
       <c r="R55" t="n">
-        <v>6861040</v>
+        <v>6861030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B59" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R59" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420549</v>
+        <v>127421194</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474427</v>
+        <v>474366</v>
       </c>
       <c r="R60" t="n">
-        <v>6861001</v>
+        <v>6861035</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6531,10 +6531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127421194</v>
+        <v>127420003</v>
       </c>
       <c r="B61" t="n">
-        <v>78778</v>
+        <v>79638</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474366</v>
+        <v>474452</v>
       </c>
       <c r="R61" t="n">
-        <v>6861035</v>
+        <v>6861105</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127420397</v>
+        <v>127421291</v>
       </c>
       <c r="B64" t="n">
-        <v>79609</v>
+        <v>79052</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474453</v>
+        <v>474358</v>
       </c>
       <c r="R64" t="n">
-        <v>6861033</v>
+        <v>6861062</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,45 +6928,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127421023</v>
+        <v>127419814</v>
       </c>
       <c r="B65" t="n">
-        <v>79609</v>
+        <v>98450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474421</v>
+        <v>474459</v>
       </c>
       <c r="R65" t="n">
-        <v>6860999</v>
+        <v>6861043</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7025,32 +7034,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127421291</v>
+        <v>127420244</v>
       </c>
       <c r="B66" t="n">
-        <v>79052</v>
+        <v>98450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,13 +7069,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474358</v>
+        <v>474425</v>
       </c>
       <c r="R66" t="n">
-        <v>6861062</v>
+        <v>6861027</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7110,19 +7119,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127419814</v>
+        <v>127421449</v>
       </c>
       <c r="B67" t="n">
         <v>98450</v>
@@ -7152,7 +7161,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7166,13 +7175,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474459</v>
+        <v>474343</v>
       </c>
       <c r="R67" t="n">
-        <v>6861043</v>
+        <v>6861086</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7216,19 +7225,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420244</v>
+        <v>127420259</v>
       </c>
       <c r="B68" t="n">
         <v>98450</v>
@@ -7256,20 +7265,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474425</v>
+        <v>474440</v>
       </c>
       <c r="R68" t="n">
-        <v>6861027</v>
+        <v>6861055</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7313,19 +7331,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127421449</v>
+        <v>127419705</v>
       </c>
       <c r="B69" t="n">
         <v>98450</v>
@@ -7353,26 +7371,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474343</v>
+        <v>474492</v>
       </c>
       <c r="R69" t="n">
-        <v>6861086</v>
+        <v>6861034</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7431,54 +7440,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420259</v>
+        <v>127420397</v>
       </c>
       <c r="B70" t="n">
-        <v>98450</v>
+        <v>79609</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474440</v>
+        <v>474453</v>
       </c>
       <c r="R70" t="n">
-        <v>6861055</v>
+        <v>6861033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127419705</v>
+        <v>127421023</v>
       </c>
       <c r="B71" t="n">
-        <v>98450</v>
+        <v>79609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474492</v>
+        <v>474421</v>
       </c>
       <c r="R71" t="n">
-        <v>6861034</v>
+        <v>6860999</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,12 +7622,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -1284,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421390</v>
+        <v>127420337</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>79052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474349</v>
+        <v>474452</v>
       </c>
       <c r="R8" t="n">
-        <v>6861060</v>
+        <v>6861042</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1355,11 +1355,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,10 +1381,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127419275</v>
+        <v>127421912</v>
       </c>
       <c r="B9" t="n">
-        <v>105488</v>
+        <v>92622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,21 +1392,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474510</v>
+        <v>474304</v>
       </c>
       <c r="R9" t="n">
-        <v>6861090</v>
+        <v>6861121</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,22 +1466,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127420396</v>
+        <v>127421390</v>
       </c>
       <c r="B10" t="n">
-        <v>78779</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1489,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474453</v>
+        <v>474349</v>
       </c>
       <c r="R10" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1554,6 +1549,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,69 +1568,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127422093</v>
+        <v>127419275</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>105488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474342</v>
+        <v>474510</v>
       </c>
       <c r="R11" t="n">
-        <v>6861153</v>
+        <v>6861090</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,44 +1665,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422309</v>
+        <v>127420396</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474479</v>
+        <v>474453</v>
       </c>
       <c r="R12" t="n">
-        <v>6861149</v>
+        <v>6861008</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,7 +1774,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419626</v>
+        <v>127422093</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1811,17 +1802,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474510</v>
+        <v>474342</v>
       </c>
       <c r="R13" t="n">
-        <v>6861060</v>
+        <v>6861153</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420337</v>
+        <v>127422309</v>
       </c>
       <c r="B14" t="n">
-        <v>79052</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474452</v>
+        <v>474479</v>
       </c>
       <c r="R14" t="n">
-        <v>6861042</v>
+        <v>6861149</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,44 +1965,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421912</v>
+        <v>127419626</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474304</v>
+        <v>474510</v>
       </c>
       <c r="R15" t="n">
-        <v>6861121</v>
+        <v>6861060</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -3067,32 +3067,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421200</v>
+        <v>127421319</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474367</v>
+        <v>474350</v>
       </c>
       <c r="R26" t="n">
-        <v>6861033</v>
+        <v>6861063</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,19 +3152,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127421319</v>
+        <v>127420359</v>
       </c>
       <c r="B27" t="n">
         <v>98450</v>
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474350</v>
+        <v>474456</v>
       </c>
       <c r="R27" t="n">
-        <v>6861063</v>
+        <v>6861021</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,19 +3249,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420359</v>
+        <v>127420283</v>
       </c>
       <c r="B28" t="n">
         <v>98450</v>
@@ -3289,20 +3289,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R28" t="n">
-        <v>6861021</v>
+        <v>6861057</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3346,19 +3355,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420283</v>
+        <v>127419889</v>
       </c>
       <c r="B29" t="n">
         <v>98450</v>
@@ -3386,29 +3395,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474434</v>
+        <v>474468</v>
       </c>
       <c r="R29" t="n">
-        <v>6861057</v>
+        <v>6861065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3452,19 +3452,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419889</v>
+        <v>127418605</v>
       </c>
       <c r="B30" t="n">
         <v>98450</v>
@@ -3492,20 +3492,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474468</v>
+        <v>474512</v>
       </c>
       <c r="R30" t="n">
-        <v>6861065</v>
+        <v>6861011</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3549,19 +3558,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127418605</v>
+        <v>127421355</v>
       </c>
       <c r="B31" t="n">
         <v>98450</v>
@@ -3591,7 +3600,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3605,13 +3614,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474512</v>
+        <v>474346</v>
       </c>
       <c r="R31" t="n">
-        <v>6861011</v>
+        <v>6861064</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3655,66 +3664,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421355</v>
+        <v>127421200</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474346</v>
+        <v>474367</v>
       </c>
       <c r="R32" t="n">
-        <v>6861064</v>
+        <v>6861033</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127418472</v>
+        <v>127419907</v>
       </c>
       <c r="B35" t="n">
-        <v>80123</v>
+        <v>78779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474510</v>
+        <v>474465</v>
       </c>
       <c r="R35" t="n">
-        <v>6861023</v>
+        <v>6861092</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4052,44 +4052,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127421991</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474302</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861119</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127418472</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474510</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861023</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127419907</v>
+        <v>127420169</v>
       </c>
       <c r="B38" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474465</v>
+        <v>474418</v>
       </c>
       <c r="R38" t="n">
-        <v>6861092</v>
+        <v>6861068</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4355,32 +4355,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127421991</v>
+        <v>127420533</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474302</v>
+        <v>474406</v>
       </c>
       <c r="R39" t="n">
-        <v>6861119</v>
+        <v>6861004</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R42" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R43" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420337</v>
+        <v>127421912</v>
       </c>
       <c r="B8" t="n">
-        <v>79052</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474452</v>
+        <v>474304</v>
       </c>
       <c r="R8" t="n">
-        <v>6861042</v>
+        <v>6861121</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,44 +1369,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421912</v>
+        <v>127420337</v>
       </c>
       <c r="B9" t="n">
-        <v>92622</v>
+        <v>79052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474304</v>
+        <v>474452</v>
       </c>
       <c r="R9" t="n">
-        <v>6861121</v>
+        <v>6861042</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419275</v>
+        <v>127422309</v>
       </c>
       <c r="B11" t="n">
-        <v>105488</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R11" t="n">
-        <v>6861090</v>
+        <v>6861149</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1665,44 +1665,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420396</v>
+        <v>127419626</v>
       </c>
       <c r="B12" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474453</v>
+        <v>474510</v>
       </c>
       <c r="R12" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127422309</v>
+        <v>127419275</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>105488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861149</v>
+        <v>6861090</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,44 +1965,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419626</v>
+        <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474510</v>
+        <v>474453</v>
       </c>
       <c r="R15" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B21" t="n">
         <v>79020</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R21" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R22" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4064,32 +4064,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127421991</v>
+        <v>127420169</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474302</v>
+        <v>474418</v>
       </c>
       <c r="R36" t="n">
-        <v>6861119</v>
+        <v>6861068</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127418472</v>
+        <v>127420533</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474510</v>
+        <v>474406</v>
       </c>
       <c r="R37" t="n">
-        <v>6861023</v>
+        <v>6861004</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420169</v>
+        <v>127418472</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474418</v>
+        <v>474510</v>
       </c>
       <c r="R38" t="n">
-        <v>6861068</v>
+        <v>6861023</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4343,22 +4343,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420533</v>
+        <v>127422311</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,13 +4390,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474406</v>
+        <v>474481</v>
       </c>
       <c r="R39" t="n">
-        <v>6861004</v>
+        <v>6861140</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4426,6 +4426,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4440,44 +4445,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127422311</v>
+        <v>127421991</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,13 +4492,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474481</v>
+        <v>474302</v>
       </c>
       <c r="R40" t="n">
-        <v>6861140</v>
+        <v>6861119</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4523,11 +4528,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R42" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R43" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5145,32 +5145,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421249</v>
+        <v>127421794</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474375</v>
+        <v>474313</v>
       </c>
       <c r="R47" t="n">
-        <v>6861033</v>
+        <v>6861110</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,19 +5230,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127420285</v>
+        <v>127421249</v>
       </c>
       <c r="B48" t="n">
         <v>98450</v>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474453</v>
+        <v>474375</v>
       </c>
       <c r="R48" t="n">
-        <v>6861049</v>
+        <v>6861033</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,19 +5327,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127421425</v>
+        <v>127420285</v>
       </c>
       <c r="B49" t="n">
         <v>98450</v>
@@ -5367,29 +5367,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R49" t="n">
-        <v>6861090</v>
+        <v>6861049</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5433,60 +5424,69 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421794</v>
+        <v>127421425</v>
       </c>
       <c r="B50" t="n">
-        <v>79052</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474313</v>
+        <v>474343</v>
       </c>
       <c r="R50" t="n">
-        <v>6861110</v>
+        <v>6861090</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5530,22 +5530,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127422256</v>
+        <v>127418980</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5553,21 +5553,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474414</v>
+        <v>474490</v>
       </c>
       <c r="R51" t="n">
-        <v>6861137</v>
+        <v>6861042</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418980</v>
+        <v>127420495</v>
       </c>
       <c r="B52" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5650,37 +5650,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474490</v>
+        <v>474434</v>
       </c>
       <c r="R52" t="n">
-        <v>6861042</v>
+        <v>6861012</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5710,6 +5715,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5724,65 +5734,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127420495</v>
+        <v>127418939</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474434</v>
+        <v>474503</v>
       </c>
       <c r="R53" t="n">
-        <v>6861012</v>
+        <v>6861040</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5812,11 +5817,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5831,19 +5831,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418939</v>
+        <v>127418408</v>
       </c>
       <c r="B54" t="n">
         <v>98450</v>
@@ -5871,17 +5871,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474503</v>
+        <v>474528</v>
       </c>
       <c r="R54" t="n">
-        <v>6861040</v>
+        <v>6861030</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,54 +5949,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418408</v>
+        <v>127422256</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474528</v>
+        <v>474414</v>
       </c>
       <c r="R55" t="n">
-        <v>6861030</v>
+        <v>6861137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127421194</v>
+        <v>127420003</v>
       </c>
       <c r="B60" t="n">
-        <v>78778</v>
+        <v>79638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474366</v>
+        <v>474452</v>
       </c>
       <c r="R60" t="n">
-        <v>6861035</v>
+        <v>6861105</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,22 +6519,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127420003</v>
+        <v>127421194</v>
       </c>
       <c r="B61" t="n">
-        <v>79638</v>
+        <v>78778</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474452</v>
+        <v>474366</v>
       </c>
       <c r="R61" t="n">
-        <v>6861105</v>
+        <v>6861035</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R63" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421291</v>
+        <v>127420397</v>
       </c>
       <c r="B64" t="n">
-        <v>79052</v>
+        <v>79609</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474358</v>
+        <v>474453</v>
       </c>
       <c r="R64" t="n">
-        <v>6861062</v>
+        <v>6861033</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,54 +6928,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127419814</v>
+        <v>127421023</v>
       </c>
       <c r="B65" t="n">
-        <v>98450</v>
+        <v>79609</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474459</v>
+        <v>474421</v>
       </c>
       <c r="R65" t="n">
-        <v>6861043</v>
+        <v>6860999</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7034,7 +7025,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420244</v>
+        <v>127419814</v>
       </c>
       <c r="B66" t="n">
         <v>98450</v>
@@ -7062,20 +7053,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474425</v>
+        <v>474459</v>
       </c>
       <c r="R66" t="n">
-        <v>6861027</v>
+        <v>6861043</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,19 +7119,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127421449</v>
+        <v>127420244</v>
       </c>
       <c r="B67" t="n">
         <v>98450</v>
@@ -7159,26 +7159,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474343</v>
+        <v>474425</v>
       </c>
       <c r="R67" t="n">
-        <v>6861086</v>
+        <v>6861027</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7237,7 +7228,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420259</v>
+        <v>127421449</v>
       </c>
       <c r="B68" t="n">
         <v>98450</v>
@@ -7267,7 +7258,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7281,13 +7272,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474440</v>
+        <v>474343</v>
       </c>
       <c r="R68" t="n">
-        <v>6861055</v>
+        <v>6861086</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7331,19 +7322,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127419705</v>
+        <v>127420259</v>
       </c>
       <c r="B69" t="n">
         <v>98450</v>
@@ -7371,20 +7362,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474492</v>
+        <v>474440</v>
       </c>
       <c r="R69" t="n">
-        <v>6861034</v>
+        <v>6861055</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,44 +7428,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420397</v>
+        <v>127419705</v>
       </c>
       <c r="B70" t="n">
-        <v>79609</v>
+        <v>98450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7475,13 +7475,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474453</v>
+        <v>474492</v>
       </c>
       <c r="R70" t="n">
-        <v>6861033</v>
+        <v>6861034</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7525,22 +7525,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127421023</v>
+        <v>127421619</v>
       </c>
       <c r="B71" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474421</v>
+        <v>474344</v>
       </c>
       <c r="R71" t="n">
-        <v>6860999</v>
+        <v>6861094</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127421372</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421912</v>
+        <v>127420396</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474304</v>
+        <v>474453</v>
       </c>
       <c r="R8" t="n">
-        <v>6861121</v>
+        <v>6861008</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421390</v>
+        <v>127421912</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>92628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474349</v>
+        <v>474304</v>
       </c>
       <c r="R10" t="n">
-        <v>6861060</v>
+        <v>6861121</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,11 +1549,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,44 +1563,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127422309</v>
+        <v>127421390</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,13 +1610,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474479</v>
+        <v>474349</v>
       </c>
       <c r="R11" t="n">
-        <v>6861149</v>
+        <v>6861060</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,6 +1646,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,22 +1665,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419626</v>
+        <v>127422093</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,17 +1705,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474510</v>
+        <v>474342</v>
       </c>
       <c r="R12" t="n">
-        <v>6861060</v>
+        <v>6861153</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1783,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422093</v>
+        <v>127422309</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,26 +1811,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474342</v>
+        <v>474479</v>
       </c>
       <c r="R13" t="n">
-        <v>6861153</v>
+        <v>6861149</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419275</v>
+        <v>127419626</v>
       </c>
       <c r="B14" t="n">
-        <v>105488</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861090</v>
+        <v>6861060</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,44 +1965,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420396</v>
+        <v>127419275</v>
       </c>
       <c r="B15" t="n">
-        <v>78779</v>
+        <v>105494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474453</v>
+        <v>474510</v>
       </c>
       <c r="R15" t="n">
-        <v>6861008</v>
+        <v>6861090</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2062,12 +2062,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
         <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B19" t="n">
-        <v>79052</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R19" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R20" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,19 +2561,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B21" t="n">
         <v>79020</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R21" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R22" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420142</v>
+        <v>127421319</v>
       </c>
       <c r="B25" t="n">
-        <v>79638</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474420</v>
+        <v>474350</v>
       </c>
       <c r="R25" t="n">
-        <v>6861097</v>
+        <v>6861063</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421319</v>
+        <v>127420359</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474350</v>
+        <v>474456</v>
       </c>
       <c r="R26" t="n">
-        <v>6861063</v>
+        <v>6861021</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,22 +3152,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420359</v>
+        <v>127420283</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3192,20 +3192,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R27" t="n">
-        <v>6861021</v>
+        <v>6861057</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,22 +3258,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420283</v>
+        <v>127419889</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3289,29 +3298,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474434</v>
+        <v>474468</v>
       </c>
       <c r="R28" t="n">
-        <v>6861057</v>
+        <v>6861065</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3355,22 +3355,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419889</v>
+        <v>127418605</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,20 +3395,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474468</v>
+        <v>474512</v>
       </c>
       <c r="R29" t="n">
-        <v>6861065</v>
+        <v>6861011</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3452,22 +3461,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127418605</v>
+        <v>127421355</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,7 +3503,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3508,13 +3517,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474512</v>
+        <v>474346</v>
       </c>
       <c r="R30" t="n">
-        <v>6861011</v>
+        <v>6861064</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3558,66 +3567,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421355</v>
+        <v>127421200</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474346</v>
+        <v>474367</v>
       </c>
       <c r="R31" t="n">
-        <v>6861064</v>
+        <v>6861033</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421200</v>
+        <v>127420142</v>
       </c>
       <c r="B32" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3687,21 +3687,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474367</v>
+        <v>474420</v>
       </c>
       <c r="R32" t="n">
-        <v>6861033</v>
+        <v>6861097</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419907</v>
+        <v>127420169</v>
       </c>
       <c r="B35" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474465</v>
+        <v>474418</v>
       </c>
       <c r="R35" t="n">
-        <v>6861092</v>
+        <v>6861068</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127420533</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474406</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861004</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127422311</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474481</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861140</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4232,6 +4232,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4246,22 +4251,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127418472</v>
+        <v>127419907</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>78779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4274,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4298,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474510</v>
+        <v>474465</v>
       </c>
       <c r="R38" t="n">
-        <v>6861023</v>
+        <v>6861092</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4343,22 +4348,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127422311</v>
+        <v>127418472</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>80123</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4371,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,13 +4395,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474481</v>
+        <v>474510</v>
       </c>
       <c r="R39" t="n">
-        <v>6861140</v>
+        <v>6861023</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4426,11 +4431,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4460,7 +4460,7 @@
         <v>127421991</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,32 +5145,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421794</v>
+        <v>127421249</v>
       </c>
       <c r="B47" t="n">
-        <v>79052</v>
+        <v>98456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474313</v>
+        <v>474375</v>
       </c>
       <c r="R47" t="n">
-        <v>6861110</v>
+        <v>6861033</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,22 +5230,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127421249</v>
+        <v>127420285</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474375</v>
+        <v>474453</v>
       </c>
       <c r="R48" t="n">
-        <v>6861033</v>
+        <v>6861049</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,22 +5327,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127420285</v>
+        <v>127421425</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,20 +5367,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474453</v>
+        <v>474343</v>
       </c>
       <c r="R49" t="n">
-        <v>6861049</v>
+        <v>6861090</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5424,69 +5433,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421425</v>
+        <v>127421794</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474343</v>
+        <v>474313</v>
       </c>
       <c r="R50" t="n">
-        <v>6861090</v>
+        <v>6861110</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5530,22 +5530,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127418980</v>
+        <v>127422256</v>
       </c>
       <c r="B51" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5553,21 +5553,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474490</v>
+        <v>474414</v>
       </c>
       <c r="R51" t="n">
-        <v>6861042</v>
+        <v>6861137</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5746,32 +5746,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127418939</v>
+        <v>127418980</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474503</v>
+        <v>474490</v>
       </c>
       <c r="R53" t="n">
-        <v>6861040</v>
+        <v>6861042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418408</v>
+        <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5871,26 +5871,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474528</v>
+        <v>474503</v>
       </c>
       <c r="R54" t="n">
-        <v>6861030</v>
+        <v>6861040</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,45 +5940,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127422256</v>
+        <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474414</v>
+        <v>474528</v>
       </c>
       <c r="R55" t="n">
-        <v>6861137</v>
+        <v>6861030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127420397</v>
+        <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474453</v>
+        <v>474344</v>
       </c>
       <c r="R64" t="n">
-        <v>6861033</v>
+        <v>6861094</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,45 +6928,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127421023</v>
+        <v>127419814</v>
       </c>
       <c r="B65" t="n">
-        <v>79609</v>
+        <v>98456</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474421</v>
+        <v>474459</v>
       </c>
       <c r="R65" t="n">
-        <v>6860999</v>
+        <v>6861043</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7025,10 +7034,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127419814</v>
+        <v>127420244</v>
       </c>
       <c r="B66" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7053,29 +7062,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474459</v>
+        <v>474425</v>
       </c>
       <c r="R66" t="n">
-        <v>6861043</v>
+        <v>6861027</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,22 +7119,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127420244</v>
+        <v>127421449</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,17 +7159,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474425</v>
+        <v>474343</v>
       </c>
       <c r="R67" t="n">
-        <v>6861027</v>
+        <v>6861086</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7228,10 +7237,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127421449</v>
+        <v>127420259</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7258,7 +7267,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7272,13 +7281,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474343</v>
+        <v>474440</v>
       </c>
       <c r="R68" t="n">
-        <v>6861086</v>
+        <v>6861055</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7322,22 +7331,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127420259</v>
+        <v>127419705</v>
       </c>
       <c r="B69" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7362,29 +7371,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474440</v>
+        <v>474492</v>
       </c>
       <c r="R69" t="n">
-        <v>6861055</v>
+        <v>6861034</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,44 +7428,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127419705</v>
+        <v>127420397</v>
       </c>
       <c r="B70" t="n">
-        <v>98450</v>
+        <v>79609</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7475,13 +7475,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474492</v>
+        <v>474453</v>
       </c>
       <c r="R70" t="n">
-        <v>6861034</v>
+        <v>6861033</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7525,22 +7525,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127421619</v>
+        <v>127421023</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474344</v>
+        <v>474421</v>
       </c>
       <c r="R71" t="n">
-        <v>6861094</v>
+        <v>6860999</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421466</v>
       </c>
       <c r="B2" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127421372</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420396</v>
+        <v>127420337</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>79055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474453</v>
+        <v>474452</v>
       </c>
       <c r="R8" t="n">
-        <v>6861008</v>
+        <v>6861042</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,44 +1369,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127420337</v>
+        <v>127421912</v>
       </c>
       <c r="B9" t="n">
-        <v>79052</v>
+        <v>92631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474452</v>
+        <v>474304</v>
       </c>
       <c r="R9" t="n">
-        <v>6861042</v>
+        <v>6861121</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1466,44 +1466,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421912</v>
+        <v>127421390</v>
       </c>
       <c r="B10" t="n">
-        <v>92628</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474304</v>
+        <v>474349</v>
       </c>
       <c r="R10" t="n">
-        <v>6861121</v>
+        <v>6861060</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,6 +1549,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,60 +1568,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127421390</v>
+        <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474349</v>
+        <v>474342</v>
       </c>
       <c r="R11" t="n">
-        <v>6861060</v>
+        <v>6861153</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,11 +1660,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,69 +1674,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422093</v>
+        <v>127419275</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>105497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474342</v>
+        <v>474510</v>
       </c>
       <c r="R12" t="n">
-        <v>6861153</v>
+        <v>6861090</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1786,7 +1786,7 @@
         <v>127422309</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>127419626</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,32 +1977,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419275</v>
+        <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>105494</v>
+        <v>78782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474510</v>
+        <v>474453</v>
       </c>
       <c r="R15" t="n">
-        <v>6861090</v>
+        <v>6861008</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2062,57 +2062,66 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420119</v>
+        <v>127418924</v>
       </c>
       <c r="B16" t="n">
-        <v>79052</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474423</v>
+        <v>474504</v>
       </c>
       <c r="R16" t="n">
-        <v>6861077</v>
+        <v>6861025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420234</v>
+        <v>127420119</v>
       </c>
       <c r="B17" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474420</v>
+        <v>474423</v>
       </c>
       <c r="R17" t="n">
-        <v>6861081</v>
+        <v>6861077</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,54 +2282,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127418924</v>
+        <v>127420234</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>79055</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474504</v>
+        <v>474420</v>
       </c>
       <c r="R18" t="n">
-        <v>6861025</v>
+        <v>6861081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>79055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R19" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>79052</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R20" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,22 +2561,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R21" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,22 +2658,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R22" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>127421319</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>127420359</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>127420283</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>127419889</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>127418605</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>127421355</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>127421200</v>
       </c>
       <c r="B31" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>127420142</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R33" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B34" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R34" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,44 +3955,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127420169</v>
+        <v>127421991</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474418</v>
+        <v>474302</v>
       </c>
       <c r="R35" t="n">
-        <v>6861068</v>
+        <v>6861119</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420533</v>
+        <v>127419907</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474406</v>
+        <v>474465</v>
       </c>
       <c r="R36" t="n">
-        <v>6861004</v>
+        <v>6861092</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127422311</v>
+        <v>127420169</v>
       </c>
       <c r="B37" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474481</v>
+        <v>474418</v>
       </c>
       <c r="R37" t="n">
-        <v>6861140</v>
+        <v>6861068</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4232,11 +4232,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4251,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127419907</v>
+        <v>127420533</v>
       </c>
       <c r="B38" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4274,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4298,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474465</v>
+        <v>474406</v>
       </c>
       <c r="R38" t="n">
-        <v>6861092</v>
+        <v>6861004</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4363,7 +4358,7 @@
         <v>127418472</v>
       </c>
       <c r="B39" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4457,32 +4452,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127421991</v>
+        <v>127422311</v>
       </c>
       <c r="B40" t="n">
-        <v>98456</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,13 +4487,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474302</v>
+        <v>474481</v>
       </c>
       <c r="R40" t="n">
-        <v>6861119</v>
+        <v>6861140</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4528,6 +4523,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421261</v>
+        <v>127422314</v>
       </c>
       <c r="B44" t="n">
-        <v>91358</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4856,21 +4856,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474359</v>
+        <v>474474</v>
       </c>
       <c r="R44" t="n">
-        <v>6861047</v>
+        <v>6861148</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4942,48 +4942,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127422314</v>
+        <v>127421641</v>
       </c>
       <c r="B45" t="n">
-        <v>57823</v>
+        <v>98459</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474474</v>
+        <v>474318</v>
       </c>
       <c r="R45" t="n">
-        <v>6861148</v>
+        <v>6861123</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5027,69 +5036,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421641</v>
+        <v>127421261</v>
       </c>
       <c r="B46" t="n">
-        <v>98456</v>
+        <v>91361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474318</v>
+        <v>474359</v>
       </c>
       <c r="R46" t="n">
-        <v>6861123</v>
+        <v>6861047</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,44 +5133,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421249</v>
+        <v>127421794</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>79055</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474375</v>
+        <v>474313</v>
       </c>
       <c r="R47" t="n">
-        <v>6861033</v>
+        <v>6861110</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,22 +5230,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127420285</v>
+        <v>127421249</v>
       </c>
       <c r="B48" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474453</v>
+        <v>474375</v>
       </c>
       <c r="R48" t="n">
-        <v>6861049</v>
+        <v>6861033</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,22 +5327,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127421425</v>
+        <v>127420285</v>
       </c>
       <c r="B49" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,29 +5367,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R49" t="n">
-        <v>6861090</v>
+        <v>6861049</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5433,60 +5424,69 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421794</v>
+        <v>127421425</v>
       </c>
       <c r="B50" t="n">
-        <v>79052</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474313</v>
+        <v>474343</v>
       </c>
       <c r="R50" t="n">
-        <v>6861110</v>
+        <v>6861090</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5530,22 +5530,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127422256</v>
+        <v>127420495</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5553,37 +5553,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474414</v>
+        <v>474434</v>
       </c>
       <c r="R51" t="n">
-        <v>6861137</v>
+        <v>6861012</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5613,6 +5618,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5627,65 +5637,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127420495</v>
+        <v>127418939</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474434</v>
+        <v>474503</v>
       </c>
       <c r="R52" t="n">
-        <v>6861012</v>
+        <v>6861040</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5715,11 +5720,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5734,57 +5734,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127418980</v>
+        <v>127418408</v>
       </c>
       <c r="B53" t="n">
-        <v>80123</v>
+        <v>98459</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474490</v>
+        <v>474528</v>
       </c>
       <c r="R53" t="n">
-        <v>6861042</v>
+        <v>6861030</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5843,32 +5852,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418939</v>
+        <v>127418980</v>
       </c>
       <c r="B54" t="n">
-        <v>98456</v>
+        <v>80126</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5878,10 +5887,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474503</v>
+        <v>474490</v>
       </c>
       <c r="R54" t="n">
-        <v>6861040</v>
+        <v>6861042</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,54 +5949,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418408</v>
+        <v>127422256</v>
       </c>
       <c r="B55" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474528</v>
+        <v>474414</v>
       </c>
       <c r="R55" t="n">
-        <v>6861030</v>
+        <v>6861137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,7 +6049,7 @@
         <v>127420040</v>
       </c>
       <c r="B56" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R59" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B60" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R60" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,12 +6519,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6534,7 +6534,7 @@
         <v>127421194</v>
       </c>
       <c r="B61" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>127419814</v>
       </c>
       <c r="B65" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>127420244</v>
       </c>
       <c r="B66" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>127421449</v>
       </c>
       <c r="B67" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>127420259</v>
       </c>
       <c r="B68" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>127419705</v>
       </c>
       <c r="B69" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>127420397</v>
       </c>
       <c r="B70" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>127421023</v>
       </c>
       <c r="B71" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,48 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127421466</v>
+        <v>127421372</v>
       </c>
       <c r="B2" t="n">
-        <v>79055</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474345</v>
+        <v>474351</v>
       </c>
       <c r="R2" t="n">
-        <v>6861089</v>
+        <v>6861066</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +784,7 @@
         <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127421372</v>
+        <v>127420823</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -913,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474351</v>
+        <v>474431</v>
       </c>
       <c r="R4" t="n">
-        <v>6861066</v>
+        <v>6860959</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,69 +972,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127420823</v>
+        <v>127421466</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>79061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474431</v>
+        <v>474345</v>
       </c>
       <c r="R5" t="n">
-        <v>6860959</v>
+        <v>6861089</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>127420337</v>
       </c>
       <c r="B8" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>127421912</v>
       </c>
       <c r="B9" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421390</v>
+        <v>127419275</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>105505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474349</v>
+        <v>474510</v>
       </c>
       <c r="R10" t="n">
-        <v>6861060</v>
+        <v>6861090</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,11 +1549,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,7 +1578,7 @@
         <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,32 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419275</v>
+        <v>127422309</v>
       </c>
       <c r="B12" t="n">
-        <v>105497</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,13 +1716,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R12" t="n">
-        <v>6861090</v>
+        <v>6861149</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,22 +1766,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422309</v>
+        <v>127419626</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861149</v>
+        <v>6861060</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1875,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419626</v>
+        <v>127420396</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>78788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474510</v>
+        <v>474453</v>
       </c>
       <c r="R14" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1977,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420396</v>
+        <v>127421390</v>
       </c>
       <c r="B15" t="n">
-        <v>78782</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1988,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,13 +2007,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474453</v>
+        <v>474349</v>
       </c>
       <c r="R15" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2048,6 +2043,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>127418924</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127420119</v>
       </c>
       <c r="B17" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>127420234</v>
       </c>
       <c r="B18" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127421588</v>
       </c>
       <c r="B19" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>127421589</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127421356</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>127421319</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420359</v>
+        <v>127420283</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,20 +3095,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R26" t="n">
-        <v>6861021</v>
+        <v>6861057</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,22 +3161,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420283</v>
+        <v>127418605</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3194,7 +3203,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3208,10 +3217,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474434</v>
+        <v>474512</v>
       </c>
       <c r="R27" t="n">
-        <v>6861057</v>
+        <v>6861011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,10 +3279,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127419889</v>
+        <v>127420359</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3305,10 +3314,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474468</v>
+        <v>474456</v>
       </c>
       <c r="R28" t="n">
-        <v>6861065</v>
+        <v>6861021</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3367,10 +3376,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127418605</v>
+        <v>127419889</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,29 +3404,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474512</v>
+        <v>474468</v>
       </c>
       <c r="R29" t="n">
-        <v>6861011</v>
+        <v>6861065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3461,12 +3461,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3476,7 +3476,7 @@
         <v>127421355</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>127421200</v>
       </c>
       <c r="B31" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>127420142</v>
       </c>
       <c r="B32" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B33" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R33" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B34" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R34" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,44 +3955,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127421991</v>
+        <v>127419907</v>
       </c>
       <c r="B35" t="n">
-        <v>98459</v>
+        <v>78788</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474302</v>
+        <v>474465</v>
       </c>
       <c r="R35" t="n">
-        <v>6861119</v>
+        <v>6861092</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127419907</v>
+        <v>127418472</v>
       </c>
       <c r="B36" t="n">
-        <v>78782</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474465</v>
+        <v>474510</v>
       </c>
       <c r="R36" t="n">
-        <v>6861092</v>
+        <v>6861023</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,12 +4149,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4164,7 +4164,7 @@
         <v>127420169</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>127420533</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127418472</v>
+        <v>127422311</v>
       </c>
       <c r="B39" t="n">
-        <v>80126</v>
+        <v>57832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,13 +4390,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474510</v>
+        <v>474481</v>
       </c>
       <c r="R39" t="n">
-        <v>6861023</v>
+        <v>6861140</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4426,6 +4426,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4452,32 +4457,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127422311</v>
+        <v>127421991</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>98467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,13 +4492,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474481</v>
+        <v>474302</v>
       </c>
       <c r="R40" t="n">
-        <v>6861140</v>
+        <v>6861119</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4523,11 +4528,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127422314</v>
+        <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>91369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4856,21 +4856,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474474</v>
+        <v>474359</v>
       </c>
       <c r="R44" t="n">
-        <v>6861148</v>
+        <v>6861047</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4945,7 +4945,7 @@
         <v>127421641</v>
       </c>
       <c r="B45" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421261</v>
+        <v>127422314</v>
       </c>
       <c r="B46" t="n">
-        <v>91361</v>
+        <v>57832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,21 +5059,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474359</v>
+        <v>474474</v>
       </c>
       <c r="R46" t="n">
-        <v>6861047</v>
+        <v>6861148</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5148,7 +5148,7 @@
         <v>127421794</v>
       </c>
       <c r="B47" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>127421249</v>
       </c>
       <c r="B48" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127420285</v>
       </c>
       <c r="B49" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>127421425</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>127420495</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5649,32 +5649,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418939</v>
+        <v>127418980</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>80132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474503</v>
+        <v>474490</v>
       </c>
       <c r="R52" t="n">
-        <v>6861040</v>
+        <v>6861042</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5746,54 +5746,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127418408</v>
+        <v>127422256</v>
       </c>
       <c r="B53" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474528</v>
+        <v>474414</v>
       </c>
       <c r="R53" t="n">
-        <v>6861030</v>
+        <v>6861137</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,32 +5843,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418980</v>
+        <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>80126</v>
+        <v>98467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5887,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474490</v>
+        <v>474503</v>
       </c>
       <c r="R54" t="n">
-        <v>6861042</v>
+        <v>6861040</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,45 +5940,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127422256</v>
+        <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474414</v>
+        <v>474528</v>
       </c>
       <c r="R55" t="n">
-        <v>6861137</v>
+        <v>6861030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,7 +6049,7 @@
         <v>127420040</v>
       </c>
       <c r="B56" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B59" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R59" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R60" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,12 +6519,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6534,7 +6534,7 @@
         <v>127421194</v>
       </c>
       <c r="B61" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>127419814</v>
       </c>
       <c r="B65" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420244</v>
+        <v>127420259</v>
       </c>
       <c r="B66" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7062,20 +7062,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474425</v>
+        <v>474440</v>
       </c>
       <c r="R66" t="n">
-        <v>6861027</v>
+        <v>6861055</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,22 +7128,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127421449</v>
+        <v>127420244</v>
       </c>
       <c r="B67" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,26 +7168,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474343</v>
+        <v>474425</v>
       </c>
       <c r="R67" t="n">
-        <v>6861086</v>
+        <v>6861027</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7237,10 +7237,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420259</v>
+        <v>127421449</v>
       </c>
       <c r="B68" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7281,13 +7281,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474440</v>
+        <v>474343</v>
       </c>
       <c r="R68" t="n">
-        <v>6861055</v>
+        <v>6861086</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7331,12 +7331,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7346,7 +7346,7 @@
         <v>127419705</v>
       </c>
       <c r="B69" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>127420397</v>
       </c>
       <c r="B70" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>127421023</v>
       </c>
       <c r="B71" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127421372</v>
+        <v>127421466</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>79061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474351</v>
+        <v>474345</v>
       </c>
       <c r="R2" t="n">
-        <v>6861066</v>
+        <v>6861089</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +775,7 @@
         <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127420823</v>
+        <v>127421372</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,7 +899,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -922,13 +913,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474431</v>
+        <v>474351</v>
       </c>
       <c r="R4" t="n">
-        <v>6860959</v>
+        <v>6861066</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,60 +963,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127421466</v>
+        <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>79061</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474345</v>
+        <v>474431</v>
       </c>
       <c r="R5" t="n">
-        <v>6861089</v>
+        <v>6860959</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>127421912</v>
       </c>
       <c r="B9" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127419275</v>
+        <v>127421390</v>
       </c>
       <c r="B10" t="n">
-        <v>105505</v>
+        <v>57832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474510</v>
+        <v>474349</v>
       </c>
       <c r="R10" t="n">
-        <v>6861090</v>
+        <v>6861060</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,6 +1549,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,7 +1583,7 @@
         <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,32 +1686,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422309</v>
+        <v>127419275</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>105506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,13 +1721,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R12" t="n">
-        <v>6861149</v>
+        <v>6861090</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,22 +1771,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419626</v>
+        <v>127422309</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,10 +1818,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R13" t="n">
-        <v>6861060</v>
+        <v>6861149</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1875,32 +1880,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420396</v>
+        <v>127419626</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474453</v>
+        <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1972,10 +1977,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421390</v>
+        <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>78788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1988,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,13 +2012,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474349</v>
+        <v>474453</v>
       </c>
       <c r="R15" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2043,11 +2048,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2062,66 +2062,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127418924</v>
+        <v>127420119</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>79061</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474504</v>
+        <v>474423</v>
       </c>
       <c r="R16" t="n">
-        <v>6861025</v>
+        <v>6861077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,7 +2171,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420119</v>
+        <v>127420234</v>
       </c>
       <c r="B17" t="n">
         <v>79061</v>
@@ -2220,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474423</v>
+        <v>474420</v>
       </c>
       <c r="R17" t="n">
-        <v>6861077</v>
+        <v>6861081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,45 +2268,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127420234</v>
+        <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>79061</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474420</v>
+        <v>474504</v>
       </c>
       <c r="R18" t="n">
-        <v>6861081</v>
+        <v>6861025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2479,7 @@
         <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R21" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R22" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127421319</v>
+        <v>127421200</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474350</v>
+        <v>474367</v>
       </c>
       <c r="R25" t="n">
-        <v>6861063</v>
+        <v>6861033</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3055,12 +3055,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
         <v>127420283</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>127418605</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3279,32 +3279,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420359</v>
+        <v>127420142</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>79647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474456</v>
+        <v>474420</v>
       </c>
       <c r="R28" t="n">
-        <v>6861021</v>
+        <v>6861097</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3364,22 +3364,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419889</v>
+        <v>127421319</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474468</v>
+        <v>474350</v>
       </c>
       <c r="R29" t="n">
-        <v>6861065</v>
+        <v>6861063</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3461,22 +3461,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127421355</v>
+        <v>127420359</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3501,26 +3501,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474346</v>
+        <v>474456</v>
       </c>
       <c r="R30" t="n">
-        <v>6861064</v>
+        <v>6861021</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3579,32 +3570,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421200</v>
+        <v>127419889</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3614,10 +3605,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474367</v>
+        <v>474468</v>
       </c>
       <c r="R31" t="n">
-        <v>6861033</v>
+        <v>6861065</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3676,48 +3667,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127420142</v>
+        <v>127421355</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474420</v>
+        <v>474346</v>
       </c>
       <c r="R32" t="n">
-        <v>6861097</v>
+        <v>6861064</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3761,22 +3761,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R33" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B34" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R34" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,12 +3955,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127418472</v>
+        <v>127420169</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474510</v>
+        <v>474418</v>
       </c>
       <c r="R36" t="n">
-        <v>6861023</v>
+        <v>6861068</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,19 +4149,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420169</v>
+        <v>127420533</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474418</v>
+        <v>474406</v>
       </c>
       <c r="R37" t="n">
-        <v>6861068</v>
+        <v>6861004</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420533</v>
+        <v>127418472</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474406</v>
+        <v>474510</v>
       </c>
       <c r="R38" t="n">
-        <v>6861004</v>
+        <v>6861023</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4343,12 +4343,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4460,7 +4460,7 @@
         <v>127421991</v>
       </c>
       <c r="B40" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4942,57 +4942,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421641</v>
+        <v>127422314</v>
       </c>
       <c r="B45" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474318</v>
+        <v>474474</v>
       </c>
       <c r="R45" t="n">
-        <v>6861123</v>
+        <v>6861148</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5036,60 +5027,69 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127422314</v>
+        <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474474</v>
+        <v>474318</v>
       </c>
       <c r="R46" t="n">
-        <v>6861148</v>
+        <v>6861123</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5133,12 +5133,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5245,7 +5245,7 @@
         <v>127421249</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127420285</v>
       </c>
       <c r="B49" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>127421425</v>
       </c>
       <c r="B50" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5649,10 +5649,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418980</v>
+        <v>127422256</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,21 +5660,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474490</v>
+        <v>474414</v>
       </c>
       <c r="R52" t="n">
-        <v>6861042</v>
+        <v>6861137</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5746,10 +5746,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127422256</v>
+        <v>127418980</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5757,21 +5757,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474414</v>
+        <v>474490</v>
       </c>
       <c r="R53" t="n">
-        <v>6861137</v>
+        <v>6861042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5846,7 +5846,7 @@
         <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R59" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B60" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R60" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,12 +6519,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421619</v>
+        <v>127420397</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474344</v>
+        <v>474453</v>
       </c>
       <c r="R64" t="n">
-        <v>6861094</v>
+        <v>6861033</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,54 +6928,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127419814</v>
+        <v>127421023</v>
       </c>
       <c r="B65" t="n">
-        <v>98467</v>
+        <v>79618</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474459</v>
+        <v>474421</v>
       </c>
       <c r="R65" t="n">
-        <v>6861043</v>
+        <v>6860999</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7034,54 +7025,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420259</v>
+        <v>127421619</v>
       </c>
       <c r="B66" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474440</v>
+        <v>474344</v>
       </c>
       <c r="R66" t="n">
-        <v>6861055</v>
+        <v>6861094</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7140,10 +7122,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127420244</v>
+        <v>127419814</v>
       </c>
       <c r="B67" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7168,20 +7150,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474425</v>
+        <v>474459</v>
       </c>
       <c r="R67" t="n">
-        <v>6861027</v>
+        <v>6861043</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7225,22 +7216,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127421449</v>
+        <v>127420244</v>
       </c>
       <c r="B68" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7265,26 +7256,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474343</v>
+        <v>474425</v>
       </c>
       <c r="R68" t="n">
-        <v>6861086</v>
+        <v>6861027</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7343,10 +7325,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127419705</v>
+        <v>127421449</v>
       </c>
       <c r="B69" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7371,17 +7353,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474492</v>
+        <v>474343</v>
       </c>
       <c r="R69" t="n">
-        <v>6861034</v>
+        <v>6861086</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7440,45 +7431,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420397</v>
+        <v>127420259</v>
       </c>
       <c r="B70" t="n">
-        <v>79618</v>
+        <v>98468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474453</v>
+        <v>474440</v>
       </c>
       <c r="R70" t="n">
-        <v>6861033</v>
+        <v>6861055</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127421023</v>
+        <v>127419705</v>
       </c>
       <c r="B71" t="n">
-        <v>79618</v>
+        <v>98468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474421</v>
+        <v>474492</v>
       </c>
       <c r="R71" t="n">
-        <v>6860999</v>
+        <v>6861034</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,12 +7622,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420337</v>
+        <v>127419275</v>
       </c>
       <c r="B8" t="n">
-        <v>79061</v>
+        <v>105506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474452</v>
+        <v>474510</v>
       </c>
       <c r="R8" t="n">
-        <v>6861042</v>
+        <v>6861090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,45 +1381,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421912</v>
+        <v>127422093</v>
       </c>
       <c r="B9" t="n">
-        <v>92640</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474304</v>
+        <v>474342</v>
       </c>
       <c r="R9" t="n">
-        <v>6861121</v>
+        <v>6861153</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,32 +1487,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421390</v>
+        <v>127422309</v>
       </c>
       <c r="B10" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1522,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474349</v>
+        <v>474479</v>
       </c>
       <c r="R10" t="n">
-        <v>6861060</v>
+        <v>6861149</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,11 +1558,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,19 +1572,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127422093</v>
+        <v>127419626</v>
       </c>
       <c r="B11" t="n">
         <v>98468</v>
@@ -1608,26 +1612,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474342</v>
+        <v>474510</v>
       </c>
       <c r="R11" t="n">
-        <v>6861153</v>
+        <v>6861060</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1686,32 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419275</v>
+        <v>127420396</v>
       </c>
       <c r="B12" t="n">
-        <v>105506</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,13 +1716,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474510</v>
+        <v>474453</v>
       </c>
       <c r="R12" t="n">
-        <v>6861090</v>
+        <v>6861008</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,44 +1766,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422309</v>
+        <v>127420337</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1818,13 +1813,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474479</v>
+        <v>474452</v>
       </c>
       <c r="R13" t="n">
-        <v>6861149</v>
+        <v>6861042</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1868,44 +1863,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419626</v>
+        <v>127421912</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>92640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474510</v>
+        <v>474304</v>
       </c>
       <c r="R14" t="n">
-        <v>6861060</v>
+        <v>6861121</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1977,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420396</v>
+        <v>127421390</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1988,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,13 +2007,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474453</v>
+        <v>474349</v>
       </c>
       <c r="R15" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2048,6 +2043,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2062,57 +2062,66 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420119</v>
+        <v>127418924</v>
       </c>
       <c r="B16" t="n">
-        <v>79061</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474423</v>
+        <v>474504</v>
       </c>
       <c r="R16" t="n">
-        <v>6861077</v>
+        <v>6861025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420234</v>
+        <v>127420119</v>
       </c>
       <c r="B17" t="n">
         <v>79061</v>
@@ -2206,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474420</v>
+        <v>474423</v>
       </c>
       <c r="R17" t="n">
-        <v>6861081</v>
+        <v>6861077</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,54 +2282,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127418924</v>
+        <v>127420234</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474504</v>
+        <v>474420</v>
       </c>
       <c r="R18" t="n">
-        <v>6861025</v>
+        <v>6861081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R21" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R22" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420283</v>
+        <v>127421319</v>
       </c>
       <c r="B26" t="n">
         <v>98468</v>
@@ -3095,26 +3095,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474434</v>
+        <v>474350</v>
       </c>
       <c r="R26" t="n">
-        <v>6861057</v>
+        <v>6861063</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3173,7 +3164,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127418605</v>
+        <v>127420359</v>
       </c>
       <c r="B27" t="n">
         <v>98468</v>
@@ -3201,29 +3192,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474512</v>
+        <v>474456</v>
       </c>
       <c r="R27" t="n">
-        <v>6861011</v>
+        <v>6861021</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3267,57 +3249,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420142</v>
+        <v>127420283</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474420</v>
+        <v>474434</v>
       </c>
       <c r="R28" t="n">
-        <v>6861097</v>
+        <v>6861057</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3376,7 +3367,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127421319</v>
+        <v>127419889</v>
       </c>
       <c r="B29" t="n">
         <v>98468</v>
@@ -3411,13 +3402,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474350</v>
+        <v>474468</v>
       </c>
       <c r="R29" t="n">
-        <v>6861063</v>
+        <v>6861065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3461,19 +3452,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127420359</v>
+        <v>127418605</v>
       </c>
       <c r="B30" t="n">
         <v>98468</v>
@@ -3501,20 +3492,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474456</v>
+        <v>474512</v>
       </c>
       <c r="R30" t="n">
-        <v>6861021</v>
+        <v>6861011</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3558,19 +3558,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127419889</v>
+        <v>127421355</v>
       </c>
       <c r="B31" t="n">
         <v>98468</v>
@@ -3598,17 +3598,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474468</v>
+        <v>474346</v>
       </c>
       <c r="R31" t="n">
-        <v>6861065</v>
+        <v>6861064</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3667,57 +3676,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421355</v>
+        <v>127420142</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474346</v>
+        <v>474420</v>
       </c>
       <c r="R32" t="n">
-        <v>6861064</v>
+        <v>6861097</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3761,22 +3761,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B33" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R33" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R34" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,12 +3955,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127422311</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474481</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861140</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4135,6 +4135,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4149,19 +4154,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127420169</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474418</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861068</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4258,10 +4263,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127418472</v>
+        <v>127420533</v>
       </c>
       <c r="B38" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4274,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4298,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474510</v>
+        <v>474406</v>
       </c>
       <c r="R38" t="n">
-        <v>6861023</v>
+        <v>6861004</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4343,22 +4348,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127422311</v>
+        <v>127418472</v>
       </c>
       <c r="B39" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4371,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,13 +4395,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474481</v>
+        <v>474510</v>
       </c>
       <c r="R39" t="n">
-        <v>6861140</v>
+        <v>6861023</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4426,11 +4431,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5649,10 +5649,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127422256</v>
+        <v>127418980</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,21 +5660,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474414</v>
+        <v>474490</v>
       </c>
       <c r="R52" t="n">
-        <v>6861137</v>
+        <v>6861042</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5746,10 +5746,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127418980</v>
+        <v>127422256</v>
       </c>
       <c r="B53" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5757,21 +5757,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474490</v>
+        <v>474414</v>
       </c>
       <c r="R53" t="n">
-        <v>6861042</v>
+        <v>6861137</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R59" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R60" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,12 +6519,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421291</v>
+        <v>127421619</v>
       </c>
       <c r="B63" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474358</v>
+        <v>474344</v>
       </c>
       <c r="R63" t="n">
-        <v>6861062</v>
+        <v>6861094</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127420397</v>
+        <v>127421291</v>
       </c>
       <c r="B64" t="n">
-        <v>79618</v>
+        <v>79061</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474453</v>
+        <v>474358</v>
       </c>
       <c r="R64" t="n">
-        <v>6861033</v>
+        <v>6861062</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,45 +6928,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127421023</v>
+        <v>127419814</v>
       </c>
       <c r="B65" t="n">
-        <v>79618</v>
+        <v>98468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474421</v>
+        <v>474459</v>
       </c>
       <c r="R65" t="n">
-        <v>6860999</v>
+        <v>6861043</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7025,32 +7034,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127421619</v>
+        <v>127420244</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,13 +7069,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474344</v>
+        <v>474425</v>
       </c>
       <c r="R66" t="n">
-        <v>6861094</v>
+        <v>6861027</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7110,19 +7119,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127419814</v>
+        <v>127421449</v>
       </c>
       <c r="B67" t="n">
         <v>98468</v>
@@ -7152,7 +7161,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7166,13 +7175,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474459</v>
+        <v>474343</v>
       </c>
       <c r="R67" t="n">
-        <v>6861043</v>
+        <v>6861086</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7216,19 +7225,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420244</v>
+        <v>127420259</v>
       </c>
       <c r="B68" t="n">
         <v>98468</v>
@@ -7256,20 +7265,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474425</v>
+        <v>474440</v>
       </c>
       <c r="R68" t="n">
-        <v>6861027</v>
+        <v>6861055</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7313,19 +7331,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127421449</v>
+        <v>127419705</v>
       </c>
       <c r="B69" t="n">
         <v>98468</v>
@@ -7353,26 +7371,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474343</v>
+        <v>474492</v>
       </c>
       <c r="R69" t="n">
-        <v>6861086</v>
+        <v>6861034</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7431,54 +7440,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420259</v>
+        <v>127421023</v>
       </c>
       <c r="B70" t="n">
-        <v>98468</v>
+        <v>79618</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474440</v>
+        <v>474421</v>
       </c>
       <c r="R70" t="n">
-        <v>6861055</v>
+        <v>6860999</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127419705</v>
+        <v>127420397</v>
       </c>
       <c r="B71" t="n">
-        <v>98468</v>
+        <v>79618</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474492</v>
+        <v>474453</v>
       </c>
       <c r="R71" t="n">
-        <v>6861034</v>
+        <v>6861033</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,12 +7622,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127421466</v>
+        <v>127420363</v>
       </c>
       <c r="B2" t="n">
-        <v>79061</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474345</v>
+        <v>474460</v>
       </c>
       <c r="R2" t="n">
-        <v>6861089</v>
+        <v>6861033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127420363</v>
+        <v>127421372</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,20 +800,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474460</v>
+        <v>474351</v>
       </c>
       <c r="R3" t="n">
-        <v>6861033</v>
+        <v>6861066</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +866,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127421372</v>
+        <v>127420823</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -913,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474351</v>
+        <v>474431</v>
       </c>
       <c r="R4" t="n">
-        <v>6861066</v>
+        <v>6860959</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,69 +972,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127420823</v>
+        <v>127421466</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474431</v>
+        <v>474345</v>
       </c>
       <c r="R5" t="n">
-        <v>6860959</v>
+        <v>6861089</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127419275</v>
+        <v>127421912</v>
       </c>
       <c r="B8" t="n">
-        <v>105506</v>
+        <v>92641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474510</v>
+        <v>474304</v>
       </c>
       <c r="R8" t="n">
-        <v>6861090</v>
+        <v>6861121</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,69 +1369,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127422093</v>
+        <v>127421390</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474342</v>
+        <v>474349</v>
       </c>
       <c r="R9" t="n">
-        <v>6861153</v>
+        <v>6861060</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1461,6 +1452,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,22 +1471,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127422309</v>
+        <v>127422093</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1515,17 +1511,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474479</v>
+        <v>474342</v>
       </c>
       <c r="R10" t="n">
-        <v>6861149</v>
+        <v>6861153</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1584,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419626</v>
+        <v>127419275</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>105507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1627,10 @@
         <v>474510</v>
       </c>
       <c r="R11" t="n">
-        <v>6861060</v>
+        <v>6861090</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,44 +1674,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420396</v>
+        <v>127422309</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474453</v>
+        <v>474479</v>
       </c>
       <c r="R12" t="n">
-        <v>6861008</v>
+        <v>6861149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,32 +1783,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420337</v>
+        <v>127419626</v>
       </c>
       <c r="B13" t="n">
-        <v>79061</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,13 +1818,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474452</v>
+        <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861042</v>
+        <v>6861060</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1863,44 +1868,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127421912</v>
+        <v>127420396</v>
       </c>
       <c r="B14" t="n">
-        <v>92640</v>
+        <v>78788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474304</v>
+        <v>474453</v>
       </c>
       <c r="R14" t="n">
-        <v>6861121</v>
+        <v>6861008</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1972,10 +1977,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421390</v>
+        <v>127420337</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>79061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1988,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,13 +2012,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474349</v>
+        <v>474452</v>
       </c>
       <c r="R15" t="n">
-        <v>6861060</v>
+        <v>6861042</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2043,11 +2048,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2074,54 +2074,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127418924</v>
+        <v>127420119</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474504</v>
+        <v>474423</v>
       </c>
       <c r="R16" t="n">
-        <v>6861025</v>
+        <v>6861077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,7 +2171,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420119</v>
+        <v>127420234</v>
       </c>
       <c r="B17" t="n">
         <v>79061</v>
@@ -2220,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474423</v>
+        <v>474420</v>
       </c>
       <c r="R17" t="n">
-        <v>6861077</v>
+        <v>6861081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,45 +2268,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127420234</v>
+        <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>79061</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474420</v>
+        <v>474504</v>
       </c>
       <c r="R18" t="n">
-        <v>6861081</v>
+        <v>6861025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2479,7 @@
         <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R21" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R22" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3067,32 +3067,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421319</v>
+        <v>127420142</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>79647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474350</v>
+        <v>474420</v>
       </c>
       <c r="R26" t="n">
-        <v>6861063</v>
+        <v>6861097</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420359</v>
+        <v>127421319</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474456</v>
+        <v>474350</v>
       </c>
       <c r="R27" t="n">
-        <v>6861021</v>
+        <v>6861063</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,22 +3249,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420283</v>
+        <v>127420359</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3289,29 +3289,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474434</v>
+        <v>474456</v>
       </c>
       <c r="R28" t="n">
-        <v>6861057</v>
+        <v>6861021</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3355,22 +3346,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419889</v>
+        <v>127420283</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,20 +3386,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474468</v>
+        <v>474434</v>
       </c>
       <c r="R29" t="n">
-        <v>6861065</v>
+        <v>6861057</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3452,22 +3452,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127418605</v>
+        <v>127419889</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3492,29 +3492,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474512</v>
+        <v>474468</v>
       </c>
       <c r="R30" t="n">
-        <v>6861011</v>
+        <v>6861065</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3558,22 +3549,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421355</v>
+        <v>127418605</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3591,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3614,13 +3605,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474346</v>
+        <v>474512</v>
       </c>
       <c r="R31" t="n">
-        <v>6861064</v>
+        <v>6861011</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3664,60 +3655,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127420142</v>
+        <v>127421355</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474420</v>
+        <v>474346</v>
       </c>
       <c r="R32" t="n">
-        <v>6861097</v>
+        <v>6861064</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3761,22 +3761,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R33" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B34" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R34" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419907</v>
+        <v>127418472</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474465</v>
+        <v>474510</v>
       </c>
       <c r="R35" t="n">
-        <v>6861092</v>
+        <v>6861023</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4052,22 +4052,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127422311</v>
+        <v>127420169</v>
       </c>
       <c r="B36" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474481</v>
+        <v>474418</v>
       </c>
       <c r="R36" t="n">
-        <v>6861140</v>
+        <v>6861068</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4135,11 +4135,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,19 +4149,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420169</v>
+        <v>127420533</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474418</v>
+        <v>474406</v>
       </c>
       <c r="R37" t="n">
-        <v>6861068</v>
+        <v>6861004</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4263,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420533</v>
+        <v>127422311</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4274,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4298,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474406</v>
+        <v>474481</v>
       </c>
       <c r="R38" t="n">
-        <v>6861004</v>
+        <v>6861140</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4334,6 +4329,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4348,44 +4348,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127418472</v>
+        <v>127421991</v>
       </c>
       <c r="B39" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4395,13 +4395,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474510</v>
+        <v>474302</v>
       </c>
       <c r="R39" t="n">
-        <v>6861023</v>
+        <v>6861119</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4445,44 +4445,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127421991</v>
+        <v>127419907</v>
       </c>
       <c r="B40" t="n">
-        <v>98468</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474302</v>
+        <v>474465</v>
       </c>
       <c r="R40" t="n">
-        <v>6861119</v>
+        <v>6861092</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R42" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R43" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4848,7 +4848,7 @@
         <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,32 +5145,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421794</v>
+        <v>127421249</v>
       </c>
       <c r="B47" t="n">
-        <v>79061</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474313</v>
+        <v>474375</v>
       </c>
       <c r="R47" t="n">
-        <v>6861110</v>
+        <v>6861033</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,22 +5230,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127421249</v>
+        <v>127420285</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474375</v>
+        <v>474453</v>
       </c>
       <c r="R48" t="n">
-        <v>6861033</v>
+        <v>6861049</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,22 +5327,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127420285</v>
+        <v>127421425</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,20 +5367,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474453</v>
+        <v>474343</v>
       </c>
       <c r="R49" t="n">
-        <v>6861049</v>
+        <v>6861090</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5424,69 +5433,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421425</v>
+        <v>127421794</v>
       </c>
       <c r="B50" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474343</v>
+        <v>474313</v>
       </c>
       <c r="R50" t="n">
-        <v>6861090</v>
+        <v>6861110</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5530,12 +5530,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
         <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R59" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B60" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R60" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,12 +6519,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6831,45 +6831,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421291</v>
+        <v>127420259</v>
       </c>
       <c r="B64" t="n">
-        <v>79061</v>
+        <v>98469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474358</v>
+        <v>474440</v>
       </c>
       <c r="R64" t="n">
-        <v>6861062</v>
+        <v>6861055</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,10 +6937,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127419814</v>
+        <v>127419705</v>
       </c>
       <c r="B65" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6956,29 +6965,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474459</v>
+        <v>474492</v>
       </c>
       <c r="R65" t="n">
-        <v>6861043</v>
+        <v>6861034</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7022,44 +7022,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420244</v>
+        <v>127421291</v>
       </c>
       <c r="B66" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7069,13 +7069,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474425</v>
+        <v>474358</v>
       </c>
       <c r="R66" t="n">
-        <v>6861027</v>
+        <v>6861062</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,22 +7119,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127421449</v>
+        <v>127419814</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474343</v>
+        <v>474459</v>
       </c>
       <c r="R67" t="n">
-        <v>6861086</v>
+        <v>6861043</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7225,22 +7225,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420259</v>
+        <v>127420244</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7265,29 +7265,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474440</v>
+        <v>474425</v>
       </c>
       <c r="R68" t="n">
-        <v>6861055</v>
+        <v>6861027</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7331,22 +7322,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127419705</v>
+        <v>127421449</v>
       </c>
       <c r="B69" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7371,17 +7362,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474492</v>
+        <v>474343</v>
       </c>
       <c r="R69" t="n">
-        <v>6861034</v>
+        <v>6861086</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127421023</v>
+        <v>127420397</v>
       </c>
       <c r="B70" t="n">
         <v>79618</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474421</v>
+        <v>474453</v>
       </c>
       <c r="R70" t="n">
-        <v>6860999</v>
+        <v>6861033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127420397</v>
+        <v>127421023</v>
       </c>
       <c r="B71" t="n">
         <v>79618</v>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474453</v>
+        <v>474421</v>
       </c>
       <c r="R71" t="n">
-        <v>6861033</v>
+        <v>6860999</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127420363</v>
+        <v>127421372</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,20 +703,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474460</v>
+        <v>474351</v>
       </c>
       <c r="R2" t="n">
-        <v>6861033</v>
+        <v>6861066</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127421372</v>
+        <v>127420363</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,29 +809,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474351</v>
+        <v>474460</v>
       </c>
       <c r="R3" t="n">
-        <v>6861066</v>
+        <v>6861033</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -881,7 +881,7 @@
         <v>127420823</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127422247</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>127422121</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421912</v>
+        <v>127422309</v>
       </c>
       <c r="B8" t="n">
-        <v>92641</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474304</v>
+        <v>474479</v>
       </c>
       <c r="R8" t="n">
-        <v>6861121</v>
+        <v>6861149</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1381,32 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421390</v>
+        <v>127419626</v>
       </c>
       <c r="B9" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474349</v>
+        <v>474510</v>
       </c>
       <c r="R9" t="n">
         <v>6861060</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,11 +1452,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,66 +1466,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127422093</v>
+        <v>127420396</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>78788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474342</v>
+        <v>474453</v>
       </c>
       <c r="R10" t="n">
-        <v>6861153</v>
+        <v>6861008</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1589,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419275</v>
+        <v>127421912</v>
       </c>
       <c r="B11" t="n">
-        <v>105507</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1610,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474510</v>
+        <v>474304</v>
       </c>
       <c r="R11" t="n">
-        <v>6861090</v>
+        <v>6861121</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,22 +1660,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422309</v>
+        <v>127422093</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,17 +1700,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474479</v>
+        <v>474342</v>
       </c>
       <c r="R12" t="n">
-        <v>6861149</v>
+        <v>6861153</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,32 +1778,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419626</v>
+        <v>127419275</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>105508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1816,10 @@
         <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861060</v>
+        <v>6861090</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1868,22 +1863,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420396</v>
+        <v>127420337</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1891,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,13 +1910,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474453</v>
+        <v>474452</v>
       </c>
       <c r="R14" t="n">
-        <v>6861008</v>
+        <v>6861042</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,22 +1960,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420337</v>
+        <v>127421390</v>
       </c>
       <c r="B15" t="n">
-        <v>79061</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1988,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,13 +2007,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474452</v>
+        <v>474349</v>
       </c>
       <c r="R15" t="n">
-        <v>6861042</v>
+        <v>6861060</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2048,6 +2043,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,7 +2271,7 @@
         <v>127418924</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B19" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R19" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>79061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R20" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,19 +2561,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421356</v>
+        <v>127421589</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474351</v>
+        <v>474343</v>
       </c>
       <c r="R21" t="n">
-        <v>6861072</v>
+        <v>6861103</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421589</v>
+        <v>127421356</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474343</v>
+        <v>474351</v>
       </c>
       <c r="R22" t="n">
-        <v>6861103</v>
+        <v>6861072</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
         <v>127422329</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127421540</v>
       </c>
       <c r="B24" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127421200</v>
+        <v>127420142</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>79647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474367</v>
+        <v>474420</v>
       </c>
       <c r="R25" t="n">
-        <v>6861033</v>
+        <v>6861097</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3055,44 +3055,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420142</v>
+        <v>127420359</v>
       </c>
       <c r="B26" t="n">
-        <v>79647</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474420</v>
+        <v>474456</v>
       </c>
       <c r="R26" t="n">
-        <v>6861097</v>
+        <v>6861021</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,22 +3152,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127421319</v>
+        <v>127418605</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3192,17 +3192,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474350</v>
+        <v>474512</v>
       </c>
       <c r="R27" t="n">
-        <v>6861063</v>
+        <v>6861011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3261,10 +3270,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420359</v>
+        <v>127421319</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3296,13 +3305,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474456</v>
+        <v>474350</v>
       </c>
       <c r="R28" t="n">
-        <v>6861021</v>
+        <v>6861063</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3346,12 +3355,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3361,7 +3370,7 @@
         <v>127420283</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3467,7 +3476,7 @@
         <v>127419889</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3561,10 +3570,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127418605</v>
+        <v>127421355</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3591,7 +3600,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3605,13 +3614,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474512</v>
+        <v>474346</v>
       </c>
       <c r="R31" t="n">
-        <v>6861011</v>
+        <v>6861064</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3655,66 +3664,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421355</v>
+        <v>127421200</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>78788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474346</v>
+        <v>474367</v>
       </c>
       <c r="R32" t="n">
-        <v>6861064</v>
+        <v>6861033</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127420175</v>
+        <v>127419787</v>
       </c>
       <c r="B33" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474407</v>
+        <v>474483</v>
       </c>
       <c r="R33" t="n">
-        <v>6861093</v>
+        <v>6861058</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3858,22 +3858,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419787</v>
+        <v>127420175</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474483</v>
+        <v>474407</v>
       </c>
       <c r="R34" t="n">
-        <v>6861058</v>
+        <v>6861093</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127418472</v>
+        <v>127419907</v>
       </c>
       <c r="B35" t="n">
-        <v>80132</v>
+        <v>78788</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474510</v>
+        <v>474465</v>
       </c>
       <c r="R35" t="n">
-        <v>6861023</v>
+        <v>6861092</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4052,22 +4052,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127418472</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474510</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861023</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,19 +4149,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127420169</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474418</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861068</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127422311</v>
+        <v>127420533</v>
       </c>
       <c r="B38" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474481</v>
+        <v>474406</v>
       </c>
       <c r="R38" t="n">
-        <v>6861140</v>
+        <v>6861004</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4329,11 +4329,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4348,44 +4343,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127421991</v>
+        <v>127422311</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>57832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4395,13 +4390,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474302</v>
+        <v>474481</v>
       </c>
       <c r="R39" t="n">
-        <v>6861119</v>
+        <v>6861140</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4431,6 +4426,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4445,44 +4445,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127419907</v>
+        <v>127421991</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474465</v>
+        <v>474302</v>
       </c>
       <c r="R40" t="n">
-        <v>6861092</v>
+        <v>6861119</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4557,7 +4557,7 @@
         <v>127419737</v>
       </c>
       <c r="B41" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B42" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R42" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R43" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4848,7 +4848,7 @@
         <v>127421261</v>
       </c>
       <c r="B44" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>127421641</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>127421249</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>127420285</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127421425</v>
       </c>
       <c r="B49" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127420495</v>
+        <v>127418980</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5553,42 +5553,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474434</v>
+        <v>474490</v>
       </c>
       <c r="R51" t="n">
-        <v>6861012</v>
+        <v>6861042</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5618,11 +5613,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5637,22 +5627,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418980</v>
+        <v>127422256</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,21 +5650,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5684,10 +5674,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474490</v>
+        <v>474414</v>
       </c>
       <c r="R52" t="n">
-        <v>6861042</v>
+        <v>6861137</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5746,10 +5736,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127422256</v>
+        <v>127420495</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5757,37 +5747,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474414</v>
+        <v>474434</v>
       </c>
       <c r="R53" t="n">
-        <v>6861137</v>
+        <v>6861012</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5817,6 +5812,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5831,12 +5831,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
         <v>127418939</v>
       </c>
       <c r="B54" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>127418408</v>
       </c>
       <c r="B55" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
         <v>127422067</v>
       </c>
       <c r="B62" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R63" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,54 +6831,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127420259</v>
+        <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474440</v>
+        <v>474344</v>
       </c>
       <c r="R64" t="n">
-        <v>6861055</v>
+        <v>6861094</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6937,10 +6928,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127419705</v>
+        <v>127420244</v>
       </c>
       <c r="B65" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6972,10 +6963,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474492</v>
+        <v>474425</v>
       </c>
       <c r="R65" t="n">
-        <v>6861034</v>
+        <v>6861027</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7034,32 +7025,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127421291</v>
+        <v>127419705</v>
       </c>
       <c r="B66" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7069,13 +7060,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474358</v>
+        <v>474492</v>
       </c>
       <c r="R66" t="n">
-        <v>6861062</v>
+        <v>6861034</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7119,12 +7110,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7134,7 +7125,7 @@
         <v>127419814</v>
       </c>
       <c r="B67" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,10 +7228,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420244</v>
+        <v>127421449</v>
       </c>
       <c r="B68" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7265,17 +7256,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474425</v>
+        <v>474343</v>
       </c>
       <c r="R68" t="n">
-        <v>6861027</v>
+        <v>6861086</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7334,10 +7334,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127421449</v>
+        <v>127420259</v>
       </c>
       <c r="B69" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474343</v>
+        <v>474440</v>
       </c>
       <c r="R69" t="n">
-        <v>6861086</v>
+        <v>6861055</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,12 +7428,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127421372</v>
+        <v>127421466</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>79061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474351</v>
+        <v>474345</v>
       </c>
       <c r="R2" t="n">
-        <v>6861066</v>
+        <v>6861089</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -878,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127420823</v>
+        <v>127421372</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -908,7 +899,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -922,13 +913,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474431</v>
+        <v>474351</v>
       </c>
       <c r="R4" t="n">
-        <v>6860959</v>
+        <v>6861066</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,60 +963,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127421466</v>
+        <v>127420823</v>
       </c>
       <c r="B5" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474345</v>
+        <v>474431</v>
       </c>
       <c r="R5" t="n">
-        <v>6861089</v>
+        <v>6860959</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1284,32 +1284,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127422309</v>
+        <v>127420337</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474479</v>
+        <v>474452</v>
       </c>
       <c r="R8" t="n">
-        <v>6861149</v>
+        <v>6861042</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,44 +1369,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127419626</v>
+        <v>127421912</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474510</v>
+        <v>474304</v>
       </c>
       <c r="R9" t="n">
-        <v>6861060</v>
+        <v>6861121</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127420396</v>
+        <v>127421390</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,21 +1489,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474453</v>
+        <v>474349</v>
       </c>
       <c r="R10" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,6 +1549,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,22 +1568,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127421912</v>
+        <v>127419275</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>105508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1610,13 +1615,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474304</v>
+        <v>474510</v>
       </c>
       <c r="R11" t="n">
-        <v>6861121</v>
+        <v>6861090</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,12 +1665,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1778,32 +1783,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419275</v>
+        <v>127422309</v>
       </c>
       <c r="B13" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,13 +1818,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474510</v>
+        <v>474479</v>
       </c>
       <c r="R13" t="n">
-        <v>6861090</v>
+        <v>6861149</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1863,44 +1868,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420337</v>
+        <v>127419626</v>
       </c>
       <c r="B14" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,13 +1915,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474452</v>
+        <v>474510</v>
       </c>
       <c r="R14" t="n">
-        <v>6861042</v>
+        <v>6861060</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1960,22 +1965,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421390</v>
+        <v>127420396</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>78788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1988,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,13 +2012,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474349</v>
+        <v>474453</v>
       </c>
       <c r="R15" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2043,11 +2048,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2379,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421569</v>
+        <v>127421588</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>79061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474330</v>
+        <v>474345</v>
       </c>
       <c r="R19" t="n">
-        <v>6861109</v>
+        <v>6861091</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,44 +2464,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421588</v>
+        <v>127421569</v>
       </c>
       <c r="B20" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474345</v>
+        <v>474330</v>
       </c>
       <c r="R20" t="n">
-        <v>6861091</v>
+        <v>6861109</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3067,32 +3067,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420359</v>
+        <v>127421200</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474456</v>
+        <v>474367</v>
       </c>
       <c r="R26" t="n">
-        <v>6861021</v>
+        <v>6861033</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127418605</v>
+        <v>127421319</v>
       </c>
       <c r="B27" t="n">
         <v>98470</v>
@@ -3192,26 +3192,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474512</v>
+        <v>474350</v>
       </c>
       <c r="R27" t="n">
-        <v>6861011</v>
+        <v>6861063</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,7 +3261,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127421319</v>
+        <v>127420359</v>
       </c>
       <c r="B28" t="n">
         <v>98470</v>
@@ -3305,13 +3296,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474350</v>
+        <v>474456</v>
       </c>
       <c r="R28" t="n">
-        <v>6861063</v>
+        <v>6861021</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3355,12 +3346,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3570,7 +3561,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421355</v>
+        <v>127418605</v>
       </c>
       <c r="B31" t="n">
         <v>98470</v>
@@ -3600,7 +3591,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3614,13 +3605,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474346</v>
+        <v>474512</v>
       </c>
       <c r="R31" t="n">
-        <v>6861064</v>
+        <v>6861011</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3664,57 +3655,66 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421200</v>
+        <v>127421355</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474367</v>
+        <v>474346</v>
       </c>
       <c r="R32" t="n">
-        <v>6861033</v>
+        <v>6861064</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3967,32 +3967,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419907</v>
+        <v>127421991</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474465</v>
+        <v>474302</v>
       </c>
       <c r="R35" t="n">
-        <v>6861092</v>
+        <v>6861119</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127418472</v>
+        <v>127420169</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,13 +4099,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474510</v>
+        <v>474418</v>
       </c>
       <c r="R36" t="n">
-        <v>6861023</v>
+        <v>6861068</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,19 +4149,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420169</v>
+        <v>127420533</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474418</v>
+        <v>474406</v>
       </c>
       <c r="R37" t="n">
-        <v>6861068</v>
+        <v>6861004</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420533</v>
+        <v>127422311</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4293,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474406</v>
+        <v>474481</v>
       </c>
       <c r="R38" t="n">
-        <v>6861004</v>
+        <v>6861140</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4329,6 +4329,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4343,22 +4348,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127422311</v>
+        <v>127419907</v>
       </c>
       <c r="B39" t="n">
-        <v>57832</v>
+        <v>78788</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4371,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,13 +4395,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474481</v>
+        <v>474465</v>
       </c>
       <c r="R39" t="n">
-        <v>6861140</v>
+        <v>6861092</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4426,11 +4431,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4445,44 +4445,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127421991</v>
+        <v>127418472</v>
       </c>
       <c r="B40" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474302</v>
+        <v>474510</v>
       </c>
       <c r="R40" t="n">
-        <v>6861119</v>
+        <v>6861023</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4542,12 +4542,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4651,32 +4651,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127421487</v>
+        <v>127419661</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474337</v>
+        <v>474501</v>
       </c>
       <c r="R42" t="n">
-        <v>6861099</v>
+        <v>6861046</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419661</v>
+        <v>127421487</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474501</v>
+        <v>474337</v>
       </c>
       <c r="R43" t="n">
-        <v>6861046</v>
+        <v>6861099</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5145,32 +5145,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421249</v>
+        <v>127421794</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>79061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474375</v>
+        <v>474313</v>
       </c>
       <c r="R47" t="n">
-        <v>6861033</v>
+        <v>6861110</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,19 +5230,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127420285</v>
+        <v>127421249</v>
       </c>
       <c r="B48" t="n">
         <v>98470</v>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474453</v>
+        <v>474375</v>
       </c>
       <c r="R48" t="n">
-        <v>6861049</v>
+        <v>6861033</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,19 +5327,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127421425</v>
+        <v>127420285</v>
       </c>
       <c r="B49" t="n">
         <v>98470</v>
@@ -5367,29 +5367,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474343</v>
+        <v>474453</v>
       </c>
       <c r="R49" t="n">
-        <v>6861090</v>
+        <v>6861049</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5433,60 +5424,69 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421794</v>
+        <v>127421425</v>
       </c>
       <c r="B50" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474313</v>
+        <v>474343</v>
       </c>
       <c r="R50" t="n">
-        <v>6861110</v>
+        <v>6861090</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5530,44 +5530,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127418980</v>
+        <v>127418939</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474490</v>
+        <v>474503</v>
       </c>
       <c r="R51" t="n">
-        <v>6861042</v>
+        <v>6861040</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5639,45 +5639,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127422256</v>
+        <v>127418408</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474414</v>
+        <v>474528</v>
       </c>
       <c r="R52" t="n">
-        <v>6861137</v>
+        <v>6861030</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5843,32 +5852,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127418939</v>
+        <v>127422256</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5878,10 +5887,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474503</v>
+        <v>474414</v>
       </c>
       <c r="R54" t="n">
-        <v>6861040</v>
+        <v>6861137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,54 +5949,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418408</v>
+        <v>127418980</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474528</v>
+        <v>474490</v>
       </c>
       <c r="R55" t="n">
-        <v>6861030</v>
+        <v>6861042</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127420420</v>
+        <v>127421435</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474459</v>
+        <v>474348</v>
       </c>
       <c r="R57" t="n">
-        <v>6861004</v>
+        <v>6861097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127421435</v>
+        <v>127420420</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474348</v>
+        <v>474459</v>
       </c>
       <c r="R58" t="n">
-        <v>6861097</v>
+        <v>6861004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420003</v>
+        <v>127420549</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6348,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474452</v>
+        <v>474427</v>
       </c>
       <c r="R59" t="n">
-        <v>6861105</v>
+        <v>6861001</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,22 +6422,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420549</v>
+        <v>127420003</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6445,21 +6445,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474427</v>
+        <v>474452</v>
       </c>
       <c r="R60" t="n">
-        <v>6861001</v>
+        <v>6861105</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,12 +6519,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421291</v>
+        <v>127421619</v>
       </c>
       <c r="B63" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474358</v>
+        <v>474344</v>
       </c>
       <c r="R63" t="n">
-        <v>6861062</v>
+        <v>6861094</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R64" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,32 +6928,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127420244</v>
+        <v>127420397</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>79618</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6963,13 +6963,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474425</v>
+        <v>474453</v>
       </c>
       <c r="R65" t="n">
-        <v>6861027</v>
+        <v>6861033</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7013,44 +7013,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127419705</v>
+        <v>127421023</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>79618</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,13 +7060,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474492</v>
+        <v>474421</v>
       </c>
       <c r="R66" t="n">
-        <v>6861034</v>
+        <v>6860999</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7110,12 +7110,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127421449</v>
+        <v>127420244</v>
       </c>
       <c r="B68" t="n">
         <v>98470</v>
@@ -7256,26 +7256,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474343</v>
+        <v>474425</v>
       </c>
       <c r="R68" t="n">
-        <v>6861086</v>
+        <v>6861027</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7334,7 +7325,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127420259</v>
+        <v>127421449</v>
       </c>
       <c r="B69" t="n">
         <v>98470</v>
@@ -7364,7 +7355,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7378,13 +7369,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474440</v>
+        <v>474343</v>
       </c>
       <c r="R69" t="n">
-        <v>6861055</v>
+        <v>6861086</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7428,57 +7419,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420397</v>
+        <v>127420259</v>
       </c>
       <c r="B70" t="n">
-        <v>79618</v>
+        <v>98470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474453</v>
+        <v>474440</v>
       </c>
       <c r="R70" t="n">
-        <v>6861033</v>
+        <v>6861055</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127421023</v>
+        <v>127419705</v>
       </c>
       <c r="B71" t="n">
-        <v>79618</v>
+        <v>98470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474421</v>
+        <v>474492</v>
       </c>
       <c r="R71" t="n">
-        <v>6860999</v>
+        <v>6861034</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,12 +7622,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -1478,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127421390</v>
+        <v>127419275</v>
       </c>
       <c r="B10" t="n">
-        <v>57832</v>
+        <v>105508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474349</v>
+        <v>474510</v>
       </c>
       <c r="R10" t="n">
-        <v>6861060</v>
+        <v>6861090</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,11 +1549,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,48 +1575,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419275</v>
+        <v>127422093</v>
       </c>
       <c r="B11" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474510</v>
+        <v>474342</v>
       </c>
       <c r="R11" t="n">
-        <v>6861090</v>
+        <v>6861153</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1665,19 +1669,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422093</v>
+        <v>127422309</v>
       </c>
       <c r="B12" t="n">
         <v>98470</v>
@@ -1705,26 +1709,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474342</v>
+        <v>474479</v>
       </c>
       <c r="R12" t="n">
-        <v>6861153</v>
+        <v>6861149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1783,7 +1778,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127422309</v>
+        <v>127419626</v>
       </c>
       <c r="B13" t="n">
         <v>98470</v>
@@ -1818,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474479</v>
+        <v>474510</v>
       </c>
       <c r="R13" t="n">
-        <v>6861149</v>
+        <v>6861060</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,32 +1875,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419626</v>
+        <v>127420396</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474510</v>
+        <v>474453</v>
       </c>
       <c r="R14" t="n">
-        <v>6861060</v>
+        <v>6861008</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1977,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420396</v>
+        <v>127421390</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1988,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2012,13 +2007,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474453</v>
+        <v>474349</v>
       </c>
       <c r="R15" t="n">
-        <v>6861008</v>
+        <v>6861060</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2048,6 +2043,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3067,32 +3067,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421200</v>
+        <v>127421319</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474367</v>
+        <v>474350</v>
       </c>
       <c r="R26" t="n">
-        <v>6861033</v>
+        <v>6861063</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,19 +3152,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127421319</v>
+        <v>127420359</v>
       </c>
       <c r="B27" t="n">
         <v>98470</v>
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474350</v>
+        <v>474456</v>
       </c>
       <c r="R27" t="n">
-        <v>6861063</v>
+        <v>6861021</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,19 +3249,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420359</v>
+        <v>127420283</v>
       </c>
       <c r="B28" t="n">
         <v>98470</v>
@@ -3289,20 +3289,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R28" t="n">
-        <v>6861021</v>
+        <v>6861057</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3346,19 +3355,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420283</v>
+        <v>127419889</v>
       </c>
       <c r="B29" t="n">
         <v>98470</v>
@@ -3386,29 +3395,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474434</v>
+        <v>474468</v>
       </c>
       <c r="R29" t="n">
-        <v>6861057</v>
+        <v>6861065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3452,19 +3452,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419889</v>
+        <v>127418605</v>
       </c>
       <c r="B30" t="n">
         <v>98470</v>
@@ -3492,20 +3492,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474468</v>
+        <v>474512</v>
       </c>
       <c r="R30" t="n">
-        <v>6861065</v>
+        <v>6861011</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3549,19 +3558,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127418605</v>
+        <v>127421355</v>
       </c>
       <c r="B31" t="n">
         <v>98470</v>
@@ -3591,7 +3600,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3605,13 +3614,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474512</v>
+        <v>474346</v>
       </c>
       <c r="R31" t="n">
-        <v>6861011</v>
+        <v>6861064</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3655,66 +3664,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421355</v>
+        <v>127421200</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474346</v>
+        <v>474367</v>
       </c>
       <c r="R32" t="n">
-        <v>6861064</v>
+        <v>6861033</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421619</v>
+        <v>127421291</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474344</v>
+        <v>474358</v>
       </c>
       <c r="R63" t="n">
-        <v>6861094</v>
+        <v>6861062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421291</v>
+        <v>127421619</v>
       </c>
       <c r="B64" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474358</v>
+        <v>474344</v>
       </c>
       <c r="R64" t="n">
-        <v>6861062</v>
+        <v>6861094</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6928,45 +6928,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127420397</v>
+        <v>127419814</v>
       </c>
       <c r="B65" t="n">
-        <v>79618</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474453</v>
+        <v>474459</v>
       </c>
       <c r="R65" t="n">
-        <v>6861033</v>
+        <v>6861043</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7025,32 +7034,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127421023</v>
+        <v>127420244</v>
       </c>
       <c r="B66" t="n">
-        <v>79618</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,13 +7069,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474421</v>
+        <v>474425</v>
       </c>
       <c r="R66" t="n">
-        <v>6860999</v>
+        <v>6861027</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7110,19 +7119,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127419814</v>
+        <v>127421449</v>
       </c>
       <c r="B67" t="n">
         <v>98470</v>
@@ -7152,7 +7161,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7166,13 +7175,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474459</v>
+        <v>474343</v>
       </c>
       <c r="R67" t="n">
-        <v>6861043</v>
+        <v>6861086</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7216,19 +7225,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420244</v>
+        <v>127420259</v>
       </c>
       <c r="B68" t="n">
         <v>98470</v>
@@ -7256,20 +7265,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474425</v>
+        <v>474440</v>
       </c>
       <c r="R68" t="n">
-        <v>6861027</v>
+        <v>6861055</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7313,19 +7331,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127421449</v>
+        <v>127419705</v>
       </c>
       <c r="B69" t="n">
         <v>98470</v>
@@ -7353,26 +7371,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474343</v>
+        <v>474492</v>
       </c>
       <c r="R69" t="n">
-        <v>6861086</v>
+        <v>6861034</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7431,54 +7440,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420259</v>
+        <v>127420397</v>
       </c>
       <c r="B70" t="n">
-        <v>98470</v>
+        <v>79618</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474440</v>
+        <v>474453</v>
       </c>
       <c r="R70" t="n">
-        <v>6861055</v>
+        <v>6861033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127419705</v>
+        <v>127421023</v>
       </c>
       <c r="B71" t="n">
-        <v>98470</v>
+        <v>79618</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474492</v>
+        <v>474421</v>
       </c>
       <c r="R71" t="n">
-        <v>6861034</v>
+        <v>6860999</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,12 +7622,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127421466</v>
+        <v>127420040</v>
       </c>
       <c r="B2" t="n">
-        <v>79061</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474345</v>
+        <v>474440</v>
       </c>
       <c r="R2" t="n">
-        <v>6861089</v>
+        <v>6861086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127420363</v>
+        <v>127420119</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474460</v>
+        <v>474423</v>
       </c>
       <c r="R3" t="n">
-        <v>6861033</v>
+        <v>6861077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,57 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127421372</v>
+        <v>127420234</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474351</v>
+        <v>474420</v>
       </c>
       <c r="R4" t="n">
-        <v>6861066</v>
+        <v>6861081</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,69 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127420823</v>
+        <v>127420337</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474431</v>
+        <v>474452</v>
       </c>
       <c r="R5" t="n">
-        <v>6860959</v>
+        <v>6861042</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,54 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127422247</v>
+        <v>127421291</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474414</v>
+        <v>474358</v>
       </c>
       <c r="R6" t="n">
-        <v>6861137</v>
+        <v>6861062</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127422121</v>
+        <v>127421466</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1222,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474373</v>
+        <v>474345</v>
       </c>
       <c r="R7" t="n">
-        <v>6861129</v>
+        <v>6861089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420337</v>
+        <v>127421588</v>
       </c>
       <c r="B8" t="n">
-        <v>79061</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474452</v>
+        <v>474345</v>
       </c>
       <c r="R8" t="n">
-        <v>6861042</v>
+        <v>6861091</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421912</v>
+        <v>127421794</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474304</v>
+        <v>474313</v>
       </c>
       <c r="R9" t="n">
-        <v>6861121</v>
+        <v>6861110</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127419275</v>
+        <v>127421912</v>
       </c>
       <c r="B10" t="n">
-        <v>105508</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474510</v>
+        <v>474304</v>
       </c>
       <c r="R10" t="n">
-        <v>6861090</v>
+        <v>6861121</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1563,66 +1536,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127422093</v>
+        <v>127421261</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474342</v>
+        <v>474359</v>
       </c>
       <c r="R11" t="n">
-        <v>6861153</v>
+        <v>6861047</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1681,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127422309</v>
+        <v>127419787</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474479</v>
+        <v>474483</v>
       </c>
       <c r="R12" t="n">
-        <v>6861149</v>
+        <v>6861058</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419626</v>
+        <v>127420169</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474510</v>
+        <v>474418</v>
       </c>
       <c r="R13" t="n">
-        <v>6861060</v>
+        <v>6861068</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1875,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420396</v>
+        <v>127420533</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474453</v>
+        <v>474406</v>
       </c>
       <c r="R14" t="n">
-        <v>6861008</v>
+        <v>6861004</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1972,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421390</v>
+        <v>127420549</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474349</v>
+        <v>474427</v>
       </c>
       <c r="R15" t="n">
-        <v>6861060</v>
+        <v>6861001</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2043,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2062,44 +2021,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420119</v>
+        <v>127421356</v>
       </c>
       <c r="B16" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2109,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474423</v>
+        <v>474351</v>
       </c>
       <c r="R16" t="n">
-        <v>6861077</v>
+        <v>6861072</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2171,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420234</v>
+        <v>127421435</v>
       </c>
       <c r="B17" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2206,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474420</v>
+        <v>474348</v>
       </c>
       <c r="R17" t="n">
-        <v>6861081</v>
+        <v>6861097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127418924</v>
+        <v>127421487</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,46 +2238,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474504</v>
+        <v>474337</v>
       </c>
       <c r="R18" t="n">
-        <v>6861025</v>
+        <v>6861099</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2348,11 +2298,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2367,44 +2312,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127421588</v>
+        <v>127421589</v>
       </c>
       <c r="B19" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,13 +2359,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474345</v>
+        <v>474343</v>
       </c>
       <c r="R19" t="n">
-        <v>6861091</v>
+        <v>6861103</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,22 +2409,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421569</v>
+        <v>127421619</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,13 +2456,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474330</v>
+        <v>474344</v>
       </c>
       <c r="R20" t="n">
-        <v>6861109</v>
+        <v>6861094</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,26 +2506,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421589</v>
+        <v>127422256</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2608,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474343</v>
+        <v>474414</v>
       </c>
       <c r="R21" t="n">
-        <v>6861103</v>
+        <v>6861137</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2658,22 +2603,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127421356</v>
+        <v>127421194</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2681,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2705,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474351</v>
+        <v>474366</v>
       </c>
       <c r="R22" t="n">
-        <v>6861072</v>
+        <v>6861035</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2755,44 +2700,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127422329</v>
+        <v>127420003</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2802,13 +2747,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474481</v>
+        <v>474452</v>
       </c>
       <c r="R23" t="n">
-        <v>6861147</v>
+        <v>6861105</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2852,69 +2797,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127421540</v>
+        <v>127420142</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474339</v>
+        <v>474420</v>
       </c>
       <c r="R24" t="n">
-        <v>6861093</v>
+        <v>6861097</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2958,22 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420142</v>
+        <v>127420175</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474420</v>
+        <v>474407</v>
       </c>
       <c r="R25" t="n">
-        <v>6861097</v>
+        <v>6861093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3067,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421319</v>
+        <v>127420420</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3102,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474350</v>
+        <v>474459</v>
       </c>
       <c r="R26" t="n">
-        <v>6861063</v>
+        <v>6861004</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3164,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420359</v>
+        <v>127418472</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3199,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474456</v>
+        <v>474510</v>
       </c>
       <c r="R27" t="n">
-        <v>6861021</v>
+        <v>6861023</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3249,66 +3185,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420283</v>
+        <v>127418980</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474434</v>
+        <v>474490</v>
       </c>
       <c r="R28" t="n">
-        <v>6861057</v>
+        <v>6861042</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419889</v>
+        <v>127421916</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3402,13 +3329,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474468</v>
+        <v>474313</v>
       </c>
       <c r="R29" t="n">
-        <v>6861065</v>
+        <v>6861172</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3438,6 +3365,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På både asp och sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3452,66 +3384,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127418605</v>
+        <v>127422012</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474512</v>
+        <v>474307</v>
       </c>
       <c r="R30" t="n">
-        <v>6861011</v>
+        <v>6861161</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3544,6 +3467,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På kapad asp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3570,42 +3498,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421355</v>
+        <v>127420495</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3614,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474346</v>
+        <v>474434</v>
       </c>
       <c r="R31" t="n">
-        <v>6861064</v>
+        <v>6861012</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3650,6 +3574,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3676,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421200</v>
+        <v>127421390</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3687,21 +3616,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3711,13 +3640,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474367</v>
+        <v>474349</v>
       </c>
       <c r="R32" t="n">
-        <v>6861033</v>
+        <v>6861060</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3747,6 +3676,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3761,22 +3695,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419787</v>
+        <v>127422311</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,21 +3718,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,13 +3742,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474483</v>
+        <v>474481</v>
       </c>
       <c r="R33" t="n">
-        <v>6861058</v>
+        <v>6861140</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3844,6 +3778,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3858,22 +3797,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127420175</v>
+        <v>127422314</v>
       </c>
       <c r="B34" t="n">
-        <v>79647</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3820,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,13 +3844,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474407</v>
+        <v>474474</v>
       </c>
       <c r="R34" t="n">
-        <v>6861093</v>
+        <v>6861148</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3894,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127421991</v>
+        <v>127418408</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,20 +3934,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474302</v>
+        <v>474528</v>
       </c>
       <c r="R35" t="n">
-        <v>6861119</v>
+        <v>6861030</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4052,60 +4000,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420169</v>
+        <v>127418605</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474418</v>
+        <v>474512</v>
       </c>
       <c r="R36" t="n">
-        <v>6861068</v>
+        <v>6861011</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,60 +4106,69 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420533</v>
+        <v>127418924</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474406</v>
+        <v>474504</v>
       </c>
       <c r="R37" t="n">
-        <v>6861004</v>
+        <v>6861025</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4232,6 +4198,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Två blommande exemplar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4246,44 +4217,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127422311</v>
+        <v>127418939</v>
       </c>
       <c r="B38" t="n">
-        <v>57832</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,13 +4264,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474481</v>
+        <v>474503</v>
       </c>
       <c r="R38" t="n">
-        <v>6861140</v>
+        <v>6861040</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4329,11 +4300,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lockläte från flera håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4360,32 +4326,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127419907</v>
+        <v>127419626</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4395,10 +4361,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474465</v>
+        <v>474510</v>
       </c>
       <c r="R39" t="n">
-        <v>6861092</v>
+        <v>6861060</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4457,32 +4423,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127418472</v>
+        <v>127419661</v>
       </c>
       <c r="B40" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4492,13 +4458,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474510</v>
+        <v>474501</v>
       </c>
       <c r="R40" t="n">
-        <v>6861023</v>
+        <v>6861046</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4542,22 +4508,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127419737</v>
+        <v>127419705</v>
       </c>
       <c r="B41" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4589,13 +4555,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474472</v>
+        <v>474492</v>
       </c>
       <c r="R41" t="n">
-        <v>6861042</v>
+        <v>6861034</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4639,22 +4605,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419661</v>
+        <v>127419737</v>
       </c>
       <c r="B42" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4686,13 +4652,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474501</v>
+        <v>474472</v>
       </c>
       <c r="R42" t="n">
-        <v>6861046</v>
+        <v>6861042</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4736,60 +4702,69 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421487</v>
+        <v>127419814</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474337</v>
+        <v>474459</v>
       </c>
       <c r="R43" t="n">
-        <v>6861099</v>
+        <v>6861043</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4833,44 +4808,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421261</v>
+        <v>127419889</v>
       </c>
       <c r="B44" t="n">
-        <v>91372</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4880,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474359</v>
+        <v>474468</v>
       </c>
       <c r="R44" t="n">
-        <v>6861047</v>
+        <v>6861065</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4942,32 +4917,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127422314</v>
+        <v>127420244</v>
       </c>
       <c r="B45" t="n">
-        <v>57832</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,10 +4952,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474474</v>
+        <v>474425</v>
       </c>
       <c r="R45" t="n">
-        <v>6861148</v>
+        <v>6861027</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5039,10 +5014,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421641</v>
+        <v>127420259</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5083,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474318</v>
+        <v>474440</v>
       </c>
       <c r="R46" t="n">
-        <v>6861123</v>
+        <v>6861055</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5145,48 +5120,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421794</v>
+        <v>127420283</v>
       </c>
       <c r="B47" t="n">
-        <v>79061</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474313</v>
+        <v>474434</v>
       </c>
       <c r="R47" t="n">
-        <v>6861110</v>
+        <v>6861057</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5230,22 +5214,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127421249</v>
+        <v>127420285</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5277,13 +5261,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474375</v>
+        <v>474453</v>
       </c>
       <c r="R48" t="n">
-        <v>6861033</v>
+        <v>6861049</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5327,22 +5311,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127420285</v>
+        <v>127420359</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5374,10 +5358,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474453</v>
+        <v>474456</v>
       </c>
       <c r="R49" t="n">
-        <v>6861049</v>
+        <v>6861021</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5436,10 +5420,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127421425</v>
+        <v>127420363</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5464,26 +5448,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474343</v>
+        <v>474460</v>
       </c>
       <c r="R50" t="n">
-        <v>6861090</v>
+        <v>6861033</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5542,10 +5517,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127418939</v>
+        <v>127420823</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5570,20 +5545,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474503</v>
+        <v>474431</v>
       </c>
       <c r="R51" t="n">
-        <v>6861040</v>
+        <v>6860959</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5639,10 +5623,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127418408</v>
+        <v>127420912</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5667,29 +5651,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474528</v>
+        <v>474419</v>
       </c>
       <c r="R52" t="n">
-        <v>6861030</v>
+        <v>6860948</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5733,50 +5708,54 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127420495</v>
+        <v>127421225</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5785,13 +5764,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474434</v>
+        <v>474354</v>
       </c>
       <c r="R53" t="n">
-        <v>6861012</v>
+        <v>6861045</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5821,11 +5800,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5840,44 +5814,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127422256</v>
+        <v>127421249</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5887,10 +5861,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474414</v>
+        <v>474375</v>
       </c>
       <c r="R54" t="n">
-        <v>6861137</v>
+        <v>6861033</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,48 +5923,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127418980</v>
+        <v>127421310</v>
       </c>
       <c r="B55" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474490</v>
+        <v>474352</v>
       </c>
       <c r="R55" t="n">
-        <v>6861042</v>
+        <v>6861053</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6034,44 +6017,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127420040</v>
+        <v>127421319</v>
       </c>
       <c r="B56" t="n">
-        <v>79061</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6081,10 +6064,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474440</v>
+        <v>474350</v>
       </c>
       <c r="R56" t="n">
-        <v>6861086</v>
+        <v>6861063</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6143,48 +6126,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127421435</v>
+        <v>127421355</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474348</v>
+        <v>474346</v>
       </c>
       <c r="R57" t="n">
-        <v>6861097</v>
+        <v>6861064</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6228,60 +6220,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127420420</v>
+        <v>127421372</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474459</v>
+        <v>474351</v>
       </c>
       <c r="R58" t="n">
-        <v>6861004</v>
+        <v>6861066</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6325,60 +6326,69 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127420549</v>
+        <v>127421425</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474427</v>
+        <v>474343</v>
       </c>
       <c r="R59" t="n">
-        <v>6861001</v>
+        <v>6861090</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6422,60 +6432,69 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127420003</v>
+        <v>127421449</v>
       </c>
       <c r="B60" t="n">
-        <v>79647</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474452</v>
+        <v>474343</v>
       </c>
       <c r="R60" t="n">
-        <v>6861105</v>
+        <v>6861086</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6519,57 +6538,66 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127421194</v>
+        <v>127421540</v>
       </c>
       <c r="B61" t="n">
-        <v>78787</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474366</v>
+        <v>474339</v>
       </c>
       <c r="R61" t="n">
-        <v>6861035</v>
+        <v>6861093</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6628,10 +6656,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127422067</v>
+        <v>127421569</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6656,26 +6684,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474331</v>
+        <v>474330</v>
       </c>
       <c r="R62" t="n">
-        <v>6861145</v>
+        <v>6861109</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6734,45 +6753,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127421291</v>
+        <v>127421641</v>
       </c>
       <c r="B63" t="n">
-        <v>79061</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474358</v>
+        <v>474318</v>
       </c>
       <c r="R63" t="n">
-        <v>6861062</v>
+        <v>6861123</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6831,32 +6859,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127421619</v>
+        <v>127421991</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,13 +6894,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474344</v>
+        <v>474302</v>
       </c>
       <c r="R64" t="n">
-        <v>6861094</v>
+        <v>6861119</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6916,22 +6944,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127419814</v>
+        <v>127422067</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6958,7 +6986,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6972,13 +7000,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474459</v>
+        <v>474331</v>
       </c>
       <c r="R65" t="n">
-        <v>6861043</v>
+        <v>6861145</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7022,22 +7050,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127420244</v>
+        <v>127422093</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7062,17 +7090,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474425</v>
+        <v>474342</v>
       </c>
       <c r="R66" t="n">
-        <v>6861027</v>
+        <v>6861153</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7131,10 +7168,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127421449</v>
+        <v>127422121</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7159,29 +7196,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älghuvudet, Älghuvudet, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474343</v>
+        <v>474373</v>
       </c>
       <c r="R67" t="n">
-        <v>6861086</v>
+        <v>6861129</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7225,22 +7253,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127420259</v>
+        <v>127422247</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7281,10 +7309,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474440</v>
+        <v>474414</v>
       </c>
       <c r="R68" t="n">
-        <v>6861055</v>
+        <v>6861137</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7343,10 +7371,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127419705</v>
+        <v>127422309</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7378,10 +7406,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474492</v>
+        <v>474479</v>
       </c>
       <c r="R69" t="n">
-        <v>6861034</v>
+        <v>6861149</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7440,32 +7468,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127420397</v>
+        <v>127422329</v>
       </c>
       <c r="B70" t="n">
-        <v>79618</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7475,13 +7503,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474453</v>
+        <v>474481</v>
       </c>
       <c r="R70" t="n">
-        <v>6861033</v>
+        <v>6861147</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7525,44 +7553,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127421023</v>
+        <v>127422377</v>
       </c>
       <c r="B71" t="n">
-        <v>79618</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7572,13 +7600,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474421</v>
+        <v>474502</v>
       </c>
       <c r="R71" t="n">
-        <v>6860999</v>
+        <v>6861127</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7622,15 +7650,597 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127419275</v>
+      </c>
+      <c r="B72" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Älghuvudet, Älghuvudet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>474510</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6861090</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127419907</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Älghuvudet, Älghuvudet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>474465</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6861092</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127420396</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Älghuvudet, Älghuvudet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>474453</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6861008</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127421200</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Älghuvudet, Älghuvudet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>474367</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6861033</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127420397</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Älghuvudet, Älghuvudet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>474453</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6861033</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127421023</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Älghuvudet, Älghuvudet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>474421</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6860999</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56499-2024 artfynd.xlsx
+++ b/artfynd/A 56499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420234</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420337</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421291</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421466</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421588</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421794</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421912</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421261</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419787</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420533</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420549</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421356</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421435</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421487</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421589</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421619</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422256</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421194</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420003</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420142</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420175</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420420</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127418472</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127418980</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421916</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3495,6 +3640,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422012</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420495</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421390</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3806,6 +3966,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422311</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3903,6 +4068,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422314</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4009,6 +4179,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127418408</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4115,6 +4290,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127418605</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4226,6 +4406,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127418924</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4323,6 +4508,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127418939</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4420,6 +4610,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419626</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4517,6 +4712,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419661</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4614,6 +4814,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419705</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4711,6 +4916,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419737</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4817,6 +5027,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419814</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4914,6 +5129,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419889</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5011,6 +5231,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420244</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5117,6 +5342,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420259</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5223,6 +5453,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420283</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5320,6 +5555,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420285</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5417,6 +5657,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420359</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5514,6 +5759,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420363</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5620,6 +5870,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420823</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5717,6 +5972,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420912</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5823,6 +6083,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421225</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5920,6 +6185,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421249</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6026,6 +6296,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421310</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6123,6 +6398,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421319</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6229,6 +6509,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421355</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6335,6 +6620,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421372</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6441,6 +6731,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421425</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6547,6 +6842,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421449</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6653,6 +6953,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421540</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6750,6 +7055,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421569</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6856,6 +7166,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421641</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6953,6 +7268,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421991</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7059,6 +7379,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422067</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7165,6 +7490,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422093</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7262,6 +7592,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422121</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7368,6 +7703,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422247</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7465,6 +7805,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422309</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7562,6 +7907,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422329</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7659,6 +8009,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422377</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7756,6 +8111,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419275</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7853,6 +8213,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419907</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7950,6 +8315,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420396</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8047,6 +8417,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421200</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8144,6 +8519,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420397</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8241,8 +8621,91 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>